--- a/artfynd/A 64805-2023 artfynd.xlsx
+++ b/artfynd/A 64805-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118942480</v>
+        <v>118942694</v>
       </c>
       <c r="B2" t="n">
-        <v>90529</v>
+        <v>90476</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>624457</v>
+        <v>624468</v>
       </c>
       <c r="R2" t="n">
-        <v>7298329</v>
+        <v>7298362</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118942381</v>
+        <v>118942308</v>
       </c>
       <c r="B3" t="n">
-        <v>90795</v>
+        <v>82270</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>658</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>624423</v>
+        <v>624431</v>
       </c>
       <c r="R3" t="n">
-        <v>7298332</v>
+        <v>7298295</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118941803</v>
+        <v>118942381</v>
       </c>
       <c r="B4" t="n">
-        <v>82270</v>
+        <v>90795</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1312</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>624381</v>
+        <v>624423</v>
       </c>
       <c r="R4" t="n">
-        <v>7298418</v>
+        <v>7298332</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118940084</v>
+        <v>118942762</v>
       </c>
       <c r="B5" t="n">
-        <v>90507</v>
+        <v>90529</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,34 +997,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Balkisberg (Balkisberg), Pi lm</t>
+          <t>Dalvastjärnen (Dalvastjärnen), Pi lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>624586</v>
+        <v>624452</v>
       </c>
       <c r="R5" t="n">
-        <v>7298607</v>
+        <v>7298419</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118941819</v>
+        <v>118940084</v>
       </c>
       <c r="B6" t="n">
-        <v>90529</v>
+        <v>90507</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,34 +1099,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Dalvastjärnen (Dalvastjärnen), Pi lm</t>
+          <t>Balkisberg (Balkisberg), Pi lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>624380</v>
+        <v>624586</v>
       </c>
       <c r="R6" t="n">
-        <v>7298393</v>
+        <v>7298607</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118941656</v>
+        <v>118941845</v>
       </c>
       <c r="B7" t="n">
-        <v>90795</v>
+        <v>79608</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,38 +1197,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>658</v>
+        <v>6464</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Balkisberg (Balkisberg), Pi lm</t>
+          <t>Dalvastjärnen (Dalvastjärnen), Pi lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>624479</v>
+        <v>624377</v>
       </c>
       <c r="R7" t="n">
-        <v>7298572</v>
+        <v>7298392</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,7 +1287,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118941737</v>
+        <v>118939241</v>
       </c>
       <c r="B8" t="n">
         <v>78573</v>
@@ -1323,14 +1323,14 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Badtsavárrie (Badtsavárrie), Pi lm</t>
+          <t>Balkisberg (Balkisberg), Pi lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>624401</v>
+        <v>624606</v>
       </c>
       <c r="R8" t="n">
-        <v>7298508</v>
+        <v>7298605</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118942245</v>
+        <v>118936910</v>
       </c>
       <c r="B9" t="n">
-        <v>78491</v>
+        <v>90511</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1405,34 +1405,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Tjakttjure (Tjakttjure), Pi lm</t>
+          <t>Balkisberg (Balkisberg), Pi lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>624392</v>
+        <v>624659</v>
       </c>
       <c r="R9" t="n">
-        <v>7298198</v>
+        <v>7298524</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118942942</v>
+        <v>118936878</v>
       </c>
       <c r="B10" t="n">
-        <v>82270</v>
+        <v>78491</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1507,21 +1507,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>624582</v>
+        <v>624645</v>
       </c>
       <c r="R10" t="n">
-        <v>7298506</v>
+        <v>7298514</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118942330</v>
+        <v>118941779</v>
       </c>
       <c r="B11" t="n">
-        <v>79608</v>
+        <v>90954</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1605,38 +1605,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6464</v>
+        <v>1209</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Dalvastjärnen (Dalvastjärnen), Pi lm</t>
+          <t>Badtsavárrie (Badtsavárrie), Pi lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>624458</v>
+        <v>624395</v>
       </c>
       <c r="R11" t="n">
-        <v>7298303</v>
+        <v>7298485</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,7 +1695,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118941713</v>
+        <v>118942245</v>
       </c>
       <c r="B12" t="n">
         <v>78491</v>
@@ -1731,14 +1731,14 @@
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Balkisberg (Balkisberg), Pi lm</t>
+          <t>Tjakttjure (Tjakttjure), Pi lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>624408</v>
+        <v>624392</v>
       </c>
       <c r="R12" t="n">
-        <v>7298513</v>
+        <v>7298198</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1797,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118936855</v>
+        <v>118938830</v>
       </c>
       <c r="B13" t="n">
-        <v>82270</v>
+        <v>90795</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1813,34 +1813,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1312</v>
+        <v>658</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Dalvastjärnen (Dalvastjärnen), Pi lm</t>
+          <t>Balkisberg (Balkisberg), Pi lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>624670</v>
+        <v>624606</v>
       </c>
       <c r="R13" t="n">
-        <v>7298506</v>
+        <v>7298573</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1883,26 +1883,6 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Picea abies</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -1919,10 +1899,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118938830</v>
+        <v>118938060</v>
       </c>
       <c r="B14" t="n">
-        <v>90795</v>
+        <v>90529</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1935,21 +1915,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1959,10 +1939,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>624606</v>
+        <v>624552</v>
       </c>
       <c r="R14" t="n">
-        <v>7298573</v>
+        <v>7298554</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2021,10 +2001,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118942067</v>
+        <v>118941613</v>
       </c>
       <c r="B15" t="n">
-        <v>78491</v>
+        <v>90529</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2037,34 +2017,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Tjakttjure (Tjakttjure), Pi lm</t>
+          <t>Balkisberg (Balkisberg), Pi lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>624287</v>
+        <v>624497</v>
       </c>
       <c r="R15" t="n">
-        <v>7298315</v>
+        <v>7298652</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2123,10 +2103,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118942590</v>
+        <v>118941323</v>
       </c>
       <c r="B16" t="n">
-        <v>90865</v>
+        <v>90511</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2135,38 +2115,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1506</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Dalvastjärnen (Dalvastjärnen), Pi lm</t>
+          <t>Balkisberg (Balkisberg), Pi lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>624471</v>
+        <v>624498</v>
       </c>
       <c r="R16" t="n">
-        <v>7298339</v>
+        <v>7298629</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2225,10 +2205,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118937638</v>
+        <v>118937317</v>
       </c>
       <c r="B17" t="n">
-        <v>90529</v>
+        <v>57290</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2241,34 +2221,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Balkisberg (Balkisberg), Pi lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>624563</v>
+        <v>624629</v>
       </c>
       <c r="R17" t="n">
-        <v>7298540</v>
+        <v>7298517</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2327,10 +2312,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118942910</v>
+        <v>118937638</v>
       </c>
       <c r="B18" t="n">
-        <v>78491</v>
+        <v>90529</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2343,21 +2328,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2367,10 +2352,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>624550</v>
+        <v>624563</v>
       </c>
       <c r="R18" t="n">
-        <v>7298507</v>
+        <v>7298540</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2429,10 +2414,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118941323</v>
+        <v>118936855</v>
       </c>
       <c r="B19" t="n">
-        <v>90511</v>
+        <v>82270</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2445,34 +2430,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Balkisberg (Balkisberg), Pi lm</t>
+          <t>Dalvastjärnen (Dalvastjärnen), Pi lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>624498</v>
+        <v>624670</v>
       </c>
       <c r="R19" t="n">
-        <v>7298629</v>
+        <v>7298506</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2515,6 +2500,26 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Picea abies</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2531,10 +2536,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118942694</v>
+        <v>118942480</v>
       </c>
       <c r="B20" t="n">
-        <v>90476</v>
+        <v>90529</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2543,25 +2548,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5447</v>
+        <v>5432</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2571,10 +2576,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>624468</v>
+        <v>624457</v>
       </c>
       <c r="R20" t="n">
-        <v>7298362</v>
+        <v>7298329</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2633,10 +2638,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118942598</v>
+        <v>118941819</v>
       </c>
       <c r="B21" t="n">
-        <v>90795</v>
+        <v>90529</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2649,21 +2654,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2673,10 +2678,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>624471</v>
+        <v>624380</v>
       </c>
       <c r="R21" t="n">
-        <v>7298339</v>
+        <v>7298393</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2735,10 +2740,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118938882</v>
+        <v>118936973</v>
       </c>
       <c r="B22" t="n">
-        <v>90511</v>
+        <v>82270</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2751,34 +2756,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Balkisberg (Balkisberg), Pi lm</t>
+          <t>Dalvastjärnen (Dalvastjärnen), Pi lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>624606</v>
+        <v>624645</v>
       </c>
       <c r="R22" t="n">
-        <v>7298573</v>
+        <v>7298510</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2837,10 +2842,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>118941613</v>
+        <v>118940936</v>
       </c>
       <c r="B23" t="n">
-        <v>90529</v>
+        <v>90507</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2853,21 +2858,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2877,10 +2882,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>624497</v>
+        <v>624506</v>
       </c>
       <c r="R23" t="n">
-        <v>7298652</v>
+        <v>7298643</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2939,10 +2944,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>118936878</v>
+        <v>118938781</v>
       </c>
       <c r="B24" t="n">
-        <v>78491</v>
+        <v>90954</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2951,25 +2956,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2979,10 +2984,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>624645</v>
+        <v>624606</v>
       </c>
       <c r="R24" t="n">
-        <v>7298514</v>
+        <v>7298573</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3025,6 +3030,26 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3041,10 +3066,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>118941785</v>
+        <v>118942942</v>
       </c>
       <c r="B25" t="n">
-        <v>90795</v>
+        <v>82270</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3057,34 +3082,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>658</v>
+        <v>1312</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Badtsavárrie (Badtsavárrie), Pi lm</t>
+          <t>Balkisberg (Balkisberg), Pi lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>624395</v>
+        <v>624582</v>
       </c>
       <c r="R25" t="n">
-        <v>7298485</v>
+        <v>7298506</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3143,10 +3168,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>118941845</v>
+        <v>118941803</v>
       </c>
       <c r="B26" t="n">
-        <v>79608</v>
+        <v>82270</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3155,25 +3180,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6464</v>
+        <v>1312</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3183,10 +3208,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>624377</v>
+        <v>624381</v>
       </c>
       <c r="R26" t="n">
-        <v>7298392</v>
+        <v>7298418</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3245,10 +3270,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>118936910</v>
+        <v>118942069</v>
       </c>
       <c r="B27" t="n">
-        <v>90511</v>
+        <v>82270</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3261,34 +3286,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Balkisberg (Balkisberg), Pi lm</t>
+          <t>Tjakttjure (Tjakttjure), Pi lm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>624659</v>
+        <v>624287</v>
       </c>
       <c r="R27" t="n">
-        <v>7298524</v>
+        <v>7298315</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3347,10 +3372,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>118938060</v>
+        <v>118939884</v>
       </c>
       <c r="B28" t="n">
-        <v>90529</v>
+        <v>78573</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3363,21 +3388,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5432</v>
+        <v>864</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3387,10 +3412,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>624552</v>
+        <v>624593</v>
       </c>
       <c r="R28" t="n">
-        <v>7298554</v>
+        <v>7298603</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3433,6 +3458,26 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>glasbjörk</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Betula pubescens</t>
+        </is>
+      </c>
+      <c r="AM28" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Betula pubescens</t>
+        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
@@ -3449,10 +3494,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>118936726</v>
+        <v>118938545</v>
       </c>
       <c r="B29" t="n">
-        <v>78491</v>
+        <v>82270</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3465,34 +3510,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Dalvastjärnen (Dalvastjärnen), Pi lm</t>
+          <t>Balkisberg (Balkisberg), Pi lm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>624698</v>
+        <v>624578</v>
       </c>
       <c r="R29" t="n">
-        <v>7298510</v>
+        <v>7298576</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3535,26 +3580,6 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
@@ -3571,10 +3596,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>118936785</v>
+        <v>118938454</v>
       </c>
       <c r="B30" t="n">
-        <v>78573</v>
+        <v>90525</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3587,34 +3612,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>864</v>
+        <v>1204</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Dalvastjärnen (Dalvastjärnen), Pi lm</t>
+          <t>Balkisberg (Balkisberg), Pi lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>624687</v>
+        <v>624580</v>
       </c>
       <c r="R30" t="n">
-        <v>7298499</v>
+        <v>7298577</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3657,26 +3682,6 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Bark of dead wood # Picea abies</t>
-        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
@@ -3693,10 +3698,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>118939241</v>
+        <v>118942330</v>
       </c>
       <c r="B31" t="n">
-        <v>78573</v>
+        <v>79608</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3705,38 +3710,38 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>864</v>
+        <v>6464</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Balkisberg (Balkisberg), Pi lm</t>
+          <t>Dalvastjärnen (Dalvastjärnen), Pi lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>624606</v>
+        <v>624458</v>
       </c>
       <c r="R31" t="n">
-        <v>7298605</v>
+        <v>7298303</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3795,10 +3800,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>118941925</v>
+        <v>118942862</v>
       </c>
       <c r="B32" t="n">
-        <v>90529</v>
+        <v>82270</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3811,34 +3816,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Badtsavárrie (Badtsavárrie), Pi lm</t>
+          <t>Dalvastjärnen (Dalvastjärnen), Pi lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>624307</v>
+        <v>624490</v>
       </c>
       <c r="R32" t="n">
-        <v>7298333</v>
+        <v>7298470</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3999,10 +4004,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>118941779</v>
+        <v>118942598</v>
       </c>
       <c r="B34" t="n">
-        <v>90954</v>
+        <v>90795</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4011,38 +4016,38 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Badtsavárrie (Badtsavárrie), Pi lm</t>
+          <t>Dalvastjärnen (Dalvastjärnen), Pi lm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>624395</v>
+        <v>624471</v>
       </c>
       <c r="R34" t="n">
-        <v>7298485</v>
+        <v>7298339</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4101,10 +4106,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>118938545</v>
+        <v>118942590</v>
       </c>
       <c r="B35" t="n">
-        <v>82270</v>
+        <v>90865</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4113,38 +4118,38 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1312</v>
+        <v>1506</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Balkisberg (Balkisberg), Pi lm</t>
+          <t>Dalvastjärnen (Dalvastjärnen), Pi lm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>624578</v>
+        <v>624471</v>
       </c>
       <c r="R35" t="n">
-        <v>7298576</v>
+        <v>7298339</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4203,10 +4208,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>118937317</v>
+        <v>118940575</v>
       </c>
       <c r="B36" t="n">
-        <v>57290</v>
+        <v>78491</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4219,39 +4224,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Balkisberg (Balkisberg), Pi lm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>624629</v>
+        <v>624545</v>
       </c>
       <c r="R36" t="n">
-        <v>7298517</v>
+        <v>7298672</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4310,10 +4310,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>118941838</v>
+        <v>118942230</v>
       </c>
       <c r="B37" t="n">
-        <v>79573</v>
+        <v>90511</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4326,21 +4326,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4350,10 +4350,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>624377</v>
+        <v>624391</v>
       </c>
       <c r="R37" t="n">
-        <v>7298392</v>
+        <v>7298231</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4396,26 +4396,6 @@
       </c>
       <c r="AG37" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ37" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK37" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO37" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
@@ -4432,10 +4412,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>118941943</v>
+        <v>118942181</v>
       </c>
       <c r="B38" t="n">
-        <v>90507</v>
+        <v>90906</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4444,38 +4424,38 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1108</v>
+        <v>4217</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Badtsavárrie (Badtsavárrie), Pi lm</t>
+          <t>Dalvastjärnen (Dalvastjärnen), Pi lm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>624292</v>
+        <v>624369</v>
       </c>
       <c r="R38" t="n">
-        <v>7298339</v>
+        <v>7298268</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4518,6 +4498,26 @@
       </c>
       <c r="AG38" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM38" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
@@ -4534,10 +4534,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>118942784</v>
+        <v>118941605</v>
       </c>
       <c r="B39" t="n">
-        <v>78491</v>
+        <v>90865</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4546,38 +4546,38 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>1506</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Dalvastjärnen (Dalvastjärnen), Pi lm</t>
+          <t>Balkisberg (Balkisberg), Pi lm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>624426</v>
+        <v>624497</v>
       </c>
       <c r="R39" t="n">
-        <v>7298414</v>
+        <v>7298652</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4620,6 +4620,26 @@
       </c>
       <c r="AG39" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM39" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
@@ -4636,10 +4656,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>118941669</v>
+        <v>118941925</v>
       </c>
       <c r="B40" t="n">
-        <v>90507</v>
+        <v>90529</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4652,34 +4672,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Balkisberg (Balkisberg), Pi lm</t>
+          <t>Badtsavárrie (Badtsavárrie), Pi lm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>624459</v>
+        <v>624307</v>
       </c>
       <c r="R40" t="n">
-        <v>7298537</v>
+        <v>7298333</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4738,10 +4758,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>118940936</v>
+        <v>118936726</v>
       </c>
       <c r="B41" t="n">
-        <v>90507</v>
+        <v>78491</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4754,34 +4774,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Balkisberg (Balkisberg), Pi lm</t>
+          <t>Dalvastjärnen (Dalvastjärnen), Pi lm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>624506</v>
+        <v>624698</v>
       </c>
       <c r="R41" t="n">
-        <v>7298643</v>
+        <v>7298510</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4824,6 +4844,26 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM41" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
@@ -4840,10 +4880,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>118941605</v>
+        <v>118941713</v>
       </c>
       <c r="B42" t="n">
-        <v>90865</v>
+        <v>78491</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4852,25 +4892,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1506</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4880,10 +4920,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>624497</v>
+        <v>624408</v>
       </c>
       <c r="R42" t="n">
-        <v>7298652</v>
+        <v>7298513</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4926,26 +4966,6 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ42" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK42" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO42" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
@@ -4962,10 +4982,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>118942308</v>
+        <v>118941656</v>
       </c>
       <c r="B43" t="n">
-        <v>82270</v>
+        <v>90795</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4978,34 +4998,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1312</v>
+        <v>658</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Dalvastjärnen (Dalvastjärnen), Pi lm</t>
+          <t>Balkisberg (Balkisberg), Pi lm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>624431</v>
+        <v>624479</v>
       </c>
       <c r="R43" t="n">
-        <v>7298295</v>
+        <v>7298572</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5064,10 +5084,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>118936973</v>
+        <v>118941943</v>
       </c>
       <c r="B44" t="n">
-        <v>82270</v>
+        <v>90507</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5080,34 +5100,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1312</v>
+        <v>1108</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Dalvastjärnen (Dalvastjärnen), Pi lm</t>
+          <t>Badtsavárrie (Badtsavárrie), Pi lm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>624645</v>
+        <v>624292</v>
       </c>
       <c r="R44" t="n">
-        <v>7298510</v>
+        <v>7298339</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5166,10 +5186,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>118938454</v>
+        <v>118941669</v>
       </c>
       <c r="B45" t="n">
-        <v>90525</v>
+        <v>90507</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5182,21 +5202,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1204</v>
+        <v>1108</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5206,10 +5226,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>624580</v>
+        <v>624459</v>
       </c>
       <c r="R45" t="n">
-        <v>7298577</v>
+        <v>7298537</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5268,10 +5288,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>118939884</v>
+        <v>118942067</v>
       </c>
       <c r="B46" t="n">
-        <v>78573</v>
+        <v>78491</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5284,34 +5304,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Balkisberg (Balkisberg), Pi lm</t>
+          <t>Tjakttjure (Tjakttjure), Pi lm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>624593</v>
+        <v>624287</v>
       </c>
       <c r="R46" t="n">
-        <v>7298603</v>
+        <v>7298315</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5354,26 +5374,6 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ46" t="inlineStr">
-        <is>
-          <t>glasbjörk</t>
-        </is>
-      </c>
-      <c r="AK46" t="inlineStr">
-        <is>
-          <t>Betula pubescens</t>
-        </is>
-      </c>
-      <c r="AM46" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO46" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Betula pubescens</t>
-        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
@@ -5390,10 +5390,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>118942230</v>
+        <v>118941785</v>
       </c>
       <c r="B47" t="n">
-        <v>90511</v>
+        <v>90795</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5406,34 +5406,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Dalvastjärnen (Dalvastjärnen), Pi lm</t>
+          <t>Badtsavárrie (Badtsavárrie), Pi lm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>624391</v>
+        <v>624395</v>
       </c>
       <c r="R47" t="n">
-        <v>7298231</v>
+        <v>7298485</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5492,10 +5492,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>118942069</v>
+        <v>118938882</v>
       </c>
       <c r="B48" t="n">
-        <v>82270</v>
+        <v>90511</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5508,34 +5508,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Tjakttjure (Tjakttjure), Pi lm</t>
+          <t>Balkisberg (Balkisberg), Pi lm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>624287</v>
+        <v>624606</v>
       </c>
       <c r="R48" t="n">
-        <v>7298315</v>
+        <v>7298573</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5594,10 +5594,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>118938781</v>
+        <v>118936785</v>
       </c>
       <c r="B49" t="n">
-        <v>90954</v>
+        <v>78573</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5606,38 +5606,38 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1209</v>
+        <v>864</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Balkisberg (Balkisberg), Pi lm</t>
+          <t>Dalvastjärnen (Dalvastjärnen), Pi lm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>624606</v>
+        <v>624687</v>
       </c>
       <c r="R49" t="n">
-        <v>7298573</v>
+        <v>7298499</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5693,12 +5693,12 @@
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Bark of dead wood # Picea abies</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -5716,10 +5716,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>118942862</v>
+        <v>118942784</v>
       </c>
       <c r="B50" t="n">
-        <v>82270</v>
+        <v>78491</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5732,21 +5732,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5756,10 +5756,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>624490</v>
+        <v>624426</v>
       </c>
       <c r="R50" t="n">
-        <v>7298470</v>
+        <v>7298414</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5818,7 +5818,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>118940575</v>
+        <v>118942910</v>
       </c>
       <c r="B51" t="n">
         <v>78491</v>
@@ -5858,10 +5858,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>624545</v>
+        <v>624550</v>
       </c>
       <c r="R51" t="n">
-        <v>7298672</v>
+        <v>7298507</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5920,10 +5920,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>118942762</v>
+        <v>118941737</v>
       </c>
       <c r="B52" t="n">
-        <v>90529</v>
+        <v>78573</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5936,34 +5936,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5432</v>
+        <v>864</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Dalvastjärnen (Dalvastjärnen), Pi lm</t>
+          <t>Badtsavárrie (Badtsavárrie), Pi lm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>624452</v>
+        <v>624401</v>
       </c>
       <c r="R52" t="n">
-        <v>7298419</v>
+        <v>7298508</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6022,10 +6022,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>118942181</v>
+        <v>118941838</v>
       </c>
       <c r="B53" t="n">
-        <v>90906</v>
+        <v>79573</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6034,25 +6034,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>4217</v>
+        <v>2081</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6062,10 +6062,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>624369</v>
+        <v>624377</v>
       </c>
       <c r="R53" t="n">
-        <v>7298268</v>
+        <v>7298392</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6111,22 +6111,22 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM53" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>

--- a/artfynd/A 64805-2023 artfynd.xlsx
+++ b/artfynd/A 64805-2023 artfynd.xlsx
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118942762</v>
+        <v>118940084</v>
       </c>
       <c r="B5" t="n">
-        <v>90529</v>
+        <v>90507</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,34 +997,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Dalvastjärnen (Dalvastjärnen), Pi lm</t>
+          <t>Balkisberg (Balkisberg), Pi lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>624452</v>
+        <v>624586</v>
       </c>
       <c r="R5" t="n">
-        <v>7298419</v>
+        <v>7298607</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118940084</v>
+        <v>118942762</v>
       </c>
       <c r="B6" t="n">
-        <v>90507</v>
+        <v>90529</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,34 +1099,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Balkisberg (Balkisberg), Pi lm</t>
+          <t>Dalvastjärnen (Dalvastjärnen), Pi lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>624586</v>
+        <v>624452</v>
       </c>
       <c r="R6" t="n">
-        <v>7298607</v>
+        <v>7298419</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118941845</v>
+        <v>118939241</v>
       </c>
       <c r="B7" t="n">
-        <v>79608</v>
+        <v>78573</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,38 +1197,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6464</v>
+        <v>864</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Dalvastjärnen (Dalvastjärnen), Pi lm</t>
+          <t>Balkisberg (Balkisberg), Pi lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>624377</v>
+        <v>624606</v>
       </c>
       <c r="R7" t="n">
-        <v>7298392</v>
+        <v>7298605</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118939241</v>
+        <v>118936910</v>
       </c>
       <c r="B8" t="n">
-        <v>78573</v>
+        <v>90511</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,21 +1303,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>864</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>624606</v>
+        <v>624659</v>
       </c>
       <c r="R8" t="n">
-        <v>7298605</v>
+        <v>7298524</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118936910</v>
+        <v>118936878</v>
       </c>
       <c r="B9" t="n">
-        <v>90511</v>
+        <v>78491</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1405,21 +1405,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>624659</v>
+        <v>624645</v>
       </c>
       <c r="R9" t="n">
-        <v>7298524</v>
+        <v>7298514</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118936878</v>
+        <v>118941845</v>
       </c>
       <c r="B10" t="n">
-        <v>78491</v>
+        <v>79608</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1503,38 +1503,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Balkisberg (Balkisberg), Pi lm</t>
+          <t>Dalvastjärnen (Dalvastjärnen), Pi lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>624645</v>
+        <v>624377</v>
       </c>
       <c r="R10" t="n">
-        <v>7298514</v>
+        <v>7298392</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -2312,7 +2312,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118937638</v>
+        <v>118942480</v>
       </c>
       <c r="B18" t="n">
         <v>90529</v>
@@ -2348,14 +2348,14 @@
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Balkisberg (Balkisberg), Pi lm</t>
+          <t>Dalvastjärnen (Dalvastjärnen), Pi lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>624563</v>
+        <v>624457</v>
       </c>
       <c r="R18" t="n">
-        <v>7298540</v>
+        <v>7298329</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2414,10 +2414,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118936855</v>
+        <v>118937638</v>
       </c>
       <c r="B19" t="n">
-        <v>82270</v>
+        <v>90529</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2430,34 +2430,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1312</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Dalvastjärnen (Dalvastjärnen), Pi lm</t>
+          <t>Balkisberg (Balkisberg), Pi lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>624670</v>
+        <v>624563</v>
       </c>
       <c r="R19" t="n">
-        <v>7298506</v>
+        <v>7298540</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2500,26 +2500,6 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Picea abies</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2536,10 +2516,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118942480</v>
+        <v>118936855</v>
       </c>
       <c r="B20" t="n">
-        <v>90529</v>
+        <v>82270</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2552,21 +2532,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2576,10 +2556,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>624457</v>
+        <v>624670</v>
       </c>
       <c r="R20" t="n">
-        <v>7298329</v>
+        <v>7298506</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2622,6 +2602,26 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Picea abies</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2944,10 +2944,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>118938781</v>
+        <v>118942942</v>
       </c>
       <c r="B24" t="n">
-        <v>90954</v>
+        <v>82270</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2956,25 +2956,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1209</v>
+        <v>1312</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2984,10 +2984,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>624606</v>
+        <v>624582</v>
       </c>
       <c r="R24" t="n">
-        <v>7298573</v>
+        <v>7298506</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3030,26 +3030,6 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3066,10 +3046,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>118942942</v>
+        <v>118938781</v>
       </c>
       <c r="B25" t="n">
-        <v>82270</v>
+        <v>90954</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3078,25 +3058,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1312</v>
+        <v>1209</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3106,10 +3086,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>624582</v>
+        <v>624606</v>
       </c>
       <c r="R25" t="n">
-        <v>7298506</v>
+        <v>7298573</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3152,6 +3132,26 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM25" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
@@ -3800,10 +3800,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>118942862</v>
+        <v>118942598</v>
       </c>
       <c r="B32" t="n">
-        <v>82270</v>
+        <v>90795</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3816,21 +3816,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1312</v>
+        <v>658</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3840,10 +3840,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>624490</v>
+        <v>624471</v>
       </c>
       <c r="R32" t="n">
-        <v>7298470</v>
+        <v>7298339</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3902,10 +3902,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>118941751</v>
+        <v>118942862</v>
       </c>
       <c r="B33" t="n">
-        <v>90525</v>
+        <v>82270</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3918,34 +3918,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1204</v>
+        <v>1312</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Badtsavárrie (Badtsavárrie), Pi lm</t>
+          <t>Dalvastjärnen (Dalvastjärnen), Pi lm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>624391</v>
+        <v>624490</v>
       </c>
       <c r="R33" t="n">
-        <v>7298510</v>
+        <v>7298470</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4004,10 +4004,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>118942598</v>
+        <v>118941751</v>
       </c>
       <c r="B34" t="n">
-        <v>90795</v>
+        <v>90525</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4020,34 +4020,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>658</v>
+        <v>1204</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Dalvastjärnen (Dalvastjärnen), Pi lm</t>
+          <t>Badtsavárrie (Badtsavárrie), Pi lm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>624471</v>
+        <v>624391</v>
       </c>
       <c r="R34" t="n">
-        <v>7298339</v>
+        <v>7298510</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4208,10 +4208,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>118940575</v>
+        <v>118942230</v>
       </c>
       <c r="B36" t="n">
-        <v>78491</v>
+        <v>90511</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4224,34 +4224,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Balkisberg (Balkisberg), Pi lm</t>
+          <t>Dalvastjärnen (Dalvastjärnen), Pi lm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>624545</v>
+        <v>624391</v>
       </c>
       <c r="R36" t="n">
-        <v>7298672</v>
+        <v>7298231</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4310,10 +4310,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>118942230</v>
+        <v>118942181</v>
       </c>
       <c r="B37" t="n">
-        <v>90511</v>
+        <v>90906</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4322,25 +4322,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1202</v>
+        <v>4217</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4350,10 +4350,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>624391</v>
+        <v>624369</v>
       </c>
       <c r="R37" t="n">
-        <v>7298231</v>
+        <v>7298268</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4396,6 +4396,26 @@
       </c>
       <c r="AG37" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM37" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
@@ -4412,10 +4432,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>118942181</v>
+        <v>118940575</v>
       </c>
       <c r="B38" t="n">
-        <v>90906</v>
+        <v>78491</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4424,38 +4444,38 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4217</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Dalvastjärnen (Dalvastjärnen), Pi lm</t>
+          <t>Balkisberg (Balkisberg), Pi lm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>624369</v>
+        <v>624545</v>
       </c>
       <c r="R38" t="n">
-        <v>7298268</v>
+        <v>7298672</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4498,26 +4518,6 @@
       </c>
       <c r="AG38" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ38" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK38" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO38" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
@@ -4534,10 +4534,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>118941605</v>
+        <v>118941925</v>
       </c>
       <c r="B39" t="n">
-        <v>90865</v>
+        <v>90529</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4546,38 +4546,38 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1506</v>
+        <v>5432</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Balkisberg (Balkisberg), Pi lm</t>
+          <t>Badtsavárrie (Badtsavárrie), Pi lm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>624497</v>
+        <v>624307</v>
       </c>
       <c r="R39" t="n">
-        <v>7298652</v>
+        <v>7298333</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4620,26 +4620,6 @@
       </c>
       <c r="AG39" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ39" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK39" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO39" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
@@ -4656,10 +4636,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>118941925</v>
+        <v>118941605</v>
       </c>
       <c r="B40" t="n">
-        <v>90529</v>
+        <v>90865</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4668,38 +4648,38 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5432</v>
+        <v>1506</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Badtsavárrie (Badtsavárrie), Pi lm</t>
+          <t>Balkisberg (Balkisberg), Pi lm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>624307</v>
+        <v>624497</v>
       </c>
       <c r="R40" t="n">
-        <v>7298333</v>
+        <v>7298652</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4742,6 +4722,26 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM40" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
@@ -4758,10 +4758,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>118936726</v>
+        <v>118941943</v>
       </c>
       <c r="B41" t="n">
-        <v>78491</v>
+        <v>90507</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4774,34 +4774,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Dalvastjärnen (Dalvastjärnen), Pi lm</t>
+          <t>Badtsavárrie (Badtsavárrie), Pi lm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>624698</v>
+        <v>624292</v>
       </c>
       <c r="R41" t="n">
-        <v>7298510</v>
+        <v>7298339</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4844,26 +4844,6 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ41" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
@@ -4880,7 +4860,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>118941713</v>
+        <v>118936726</v>
       </c>
       <c r="B42" t="n">
         <v>78491</v>
@@ -4916,14 +4896,14 @@
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Balkisberg (Balkisberg), Pi lm</t>
+          <t>Dalvastjärnen (Dalvastjärnen), Pi lm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>624408</v>
+        <v>624698</v>
       </c>
       <c r="R42" t="n">
-        <v>7298513</v>
+        <v>7298510</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4966,6 +4946,26 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM42" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
@@ -4982,10 +4982,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>118941656</v>
+        <v>118941713</v>
       </c>
       <c r="B43" t="n">
-        <v>90795</v>
+        <v>78491</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4998,21 +4998,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5022,10 +5022,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>624479</v>
+        <v>624408</v>
       </c>
       <c r="R43" t="n">
-        <v>7298572</v>
+        <v>7298513</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5084,10 +5084,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>118941943</v>
+        <v>118941656</v>
       </c>
       <c r="B44" t="n">
-        <v>90507</v>
+        <v>90795</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5100,34 +5100,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1108</v>
+        <v>658</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Badtsavárrie (Badtsavárrie), Pi lm</t>
+          <t>Balkisberg (Balkisberg), Pi lm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>624292</v>
+        <v>624479</v>
       </c>
       <c r="R44" t="n">
-        <v>7298339</v>
+        <v>7298572</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5492,10 +5492,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>118938882</v>
+        <v>118942784</v>
       </c>
       <c r="B48" t="n">
-        <v>90511</v>
+        <v>78491</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5508,34 +5508,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Balkisberg (Balkisberg), Pi lm</t>
+          <t>Dalvastjärnen (Dalvastjärnen), Pi lm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>624606</v>
+        <v>624426</v>
       </c>
       <c r="R48" t="n">
-        <v>7298573</v>
+        <v>7298414</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5594,10 +5594,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>118936785</v>
+        <v>118938882</v>
       </c>
       <c r="B49" t="n">
-        <v>78573</v>
+        <v>90511</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5610,34 +5610,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>864</v>
+        <v>1202</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Dalvastjärnen (Dalvastjärnen), Pi lm</t>
+          <t>Balkisberg (Balkisberg), Pi lm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>624687</v>
+        <v>624606</v>
       </c>
       <c r="R49" t="n">
-        <v>7298499</v>
+        <v>7298573</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5680,26 +5680,6 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ49" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK49" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM49" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO49" t="inlineStr">
-        <is>
-          <t>Bark of dead wood # Picea abies</t>
-        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
@@ -5716,10 +5696,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>118942784</v>
+        <v>118936785</v>
       </c>
       <c r="B50" t="n">
-        <v>78491</v>
+        <v>78573</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5732,21 +5712,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5756,10 +5736,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>624426</v>
+        <v>624687</v>
       </c>
       <c r="R50" t="n">
-        <v>7298414</v>
+        <v>7298499</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5802,6 +5782,26 @@
       </c>
       <c r="AG50" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM50" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Picea abies</t>
+        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">

--- a/artfynd/A 64805-2023 artfynd.xlsx
+++ b/artfynd/A 64805-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118942694</v>
+        <v>118942067</v>
       </c>
       <c r="B2" t="n">
-        <v>90476</v>
+        <v>78491</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Dalvastjärnen (Dalvastjärnen), Pi lm</t>
+          <t>Tjakttjure (Tjakttjure), Pi lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>624468</v>
+        <v>624287</v>
       </c>
       <c r="R2" t="n">
-        <v>7298362</v>
+        <v>7298315</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118942308</v>
+        <v>118940084</v>
       </c>
       <c r="B3" t="n">
-        <v>82270</v>
+        <v>90507</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,34 +793,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1312</v>
+        <v>1108</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Dalvastjärnen (Dalvastjärnen), Pi lm</t>
+          <t>Balkisberg (Balkisberg), Pi lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>624431</v>
+        <v>624586</v>
       </c>
       <c r="R3" t="n">
-        <v>7298295</v>
+        <v>7298607</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118942381</v>
+        <v>118942862</v>
       </c>
       <c r="B4" t="n">
-        <v>90795</v>
+        <v>82270</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>658</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>624423</v>
+        <v>624490</v>
       </c>
       <c r="R4" t="n">
-        <v>7298332</v>
+        <v>7298470</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118940084</v>
+        <v>118942784</v>
       </c>
       <c r="B5" t="n">
-        <v>90507</v>
+        <v>78491</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,34 +997,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Balkisberg (Balkisberg), Pi lm</t>
+          <t>Dalvastjärnen (Dalvastjärnen), Pi lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>624586</v>
+        <v>624426</v>
       </c>
       <c r="R5" t="n">
-        <v>7298607</v>
+        <v>7298414</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118942762</v>
+        <v>118941713</v>
       </c>
       <c r="B6" t="n">
-        <v>90529</v>
+        <v>78491</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,34 +1099,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Dalvastjärnen (Dalvastjärnen), Pi lm</t>
+          <t>Balkisberg (Balkisberg), Pi lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>624452</v>
+        <v>624408</v>
       </c>
       <c r="R6" t="n">
-        <v>7298419</v>
+        <v>7298513</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118939241</v>
+        <v>118938781</v>
       </c>
       <c r="B7" t="n">
-        <v>78573</v>
+        <v>90954</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,25 +1197,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>864</v>
+        <v>1209</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1228,7 +1228,7 @@
         <v>624606</v>
       </c>
       <c r="R7" t="n">
-        <v>7298605</v>
+        <v>7298573</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1271,6 +1271,26 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1287,10 +1307,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118936910</v>
+        <v>118942590</v>
       </c>
       <c r="B8" t="n">
-        <v>90511</v>
+        <v>90865</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1299,38 +1319,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>1506</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Balkisberg (Balkisberg), Pi lm</t>
+          <t>Dalvastjärnen (Dalvastjärnen), Pi lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>624659</v>
+        <v>624471</v>
       </c>
       <c r="R8" t="n">
-        <v>7298524</v>
+        <v>7298339</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,10 +1409,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118936878</v>
+        <v>118942694</v>
       </c>
       <c r="B9" t="n">
-        <v>78491</v>
+        <v>90476</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1401,38 +1421,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Balkisberg (Balkisberg), Pi lm</t>
+          <t>Dalvastjärnen (Dalvastjärnen), Pi lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>624645</v>
+        <v>624468</v>
       </c>
       <c r="R9" t="n">
-        <v>7298514</v>
+        <v>7298362</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,10 +1511,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118941845</v>
+        <v>118938545</v>
       </c>
       <c r="B10" t="n">
-        <v>79608</v>
+        <v>82270</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1503,38 +1523,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6464</v>
+        <v>1312</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Dalvastjärnen (Dalvastjärnen), Pi lm</t>
+          <t>Balkisberg (Balkisberg), Pi lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>624377</v>
+        <v>624578</v>
       </c>
       <c r="R10" t="n">
-        <v>7298392</v>
+        <v>7298576</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,10 +1613,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118941779</v>
+        <v>118942181</v>
       </c>
       <c r="B11" t="n">
-        <v>90954</v>
+        <v>90906</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1605,38 +1625,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1209</v>
+        <v>4217</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Badtsavárrie (Badtsavárrie), Pi lm</t>
+          <t>Dalvastjärnen (Dalvastjärnen), Pi lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>624395</v>
+        <v>624369</v>
       </c>
       <c r="R11" t="n">
-        <v>7298485</v>
+        <v>7298268</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1679,6 +1699,26 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1695,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118942245</v>
+        <v>118942480</v>
       </c>
       <c r="B12" t="n">
-        <v>78491</v>
+        <v>90529</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1711,34 +1751,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Tjakttjure (Tjakttjure), Pi lm</t>
+          <t>Dalvastjärnen (Dalvastjärnen), Pi lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>624392</v>
+        <v>624457</v>
       </c>
       <c r="R12" t="n">
-        <v>7298198</v>
+        <v>7298329</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1797,10 +1837,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118938830</v>
+        <v>118938454</v>
       </c>
       <c r="B13" t="n">
-        <v>90795</v>
+        <v>90525</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1813,21 +1853,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>658</v>
+        <v>1204</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,10 +1877,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>624606</v>
+        <v>624580</v>
       </c>
       <c r="R13" t="n">
-        <v>7298573</v>
+        <v>7298577</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1899,10 +1939,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118938060</v>
+        <v>118942330</v>
       </c>
       <c r="B14" t="n">
-        <v>90529</v>
+        <v>79608</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1911,38 +1951,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>6464</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Balkisberg (Balkisberg), Pi lm</t>
+          <t>Dalvastjärnen (Dalvastjärnen), Pi lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>624552</v>
+        <v>624458</v>
       </c>
       <c r="R14" t="n">
-        <v>7298554</v>
+        <v>7298303</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2001,10 +2041,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118941613</v>
+        <v>118936910</v>
       </c>
       <c r="B15" t="n">
-        <v>90529</v>
+        <v>90511</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2017,21 +2057,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2041,10 +2081,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>624497</v>
+        <v>624659</v>
       </c>
       <c r="R15" t="n">
-        <v>7298652</v>
+        <v>7298524</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2103,10 +2143,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118941323</v>
+        <v>118941785</v>
       </c>
       <c r="B16" t="n">
-        <v>90511</v>
+        <v>90795</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2119,34 +2159,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Balkisberg (Balkisberg), Pi lm</t>
+          <t>Badtsavárrie (Badtsavárrie), Pi lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>624498</v>
+        <v>624395</v>
       </c>
       <c r="R16" t="n">
-        <v>7298629</v>
+        <v>7298485</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2205,10 +2245,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118937317</v>
+        <v>118938830</v>
       </c>
       <c r="B17" t="n">
-        <v>57290</v>
+        <v>90795</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2221,39 +2261,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Balkisberg (Balkisberg), Pi lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>624629</v>
+        <v>624606</v>
       </c>
       <c r="R17" t="n">
-        <v>7298517</v>
+        <v>7298573</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2312,10 +2347,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118942480</v>
+        <v>118936726</v>
       </c>
       <c r="B18" t="n">
-        <v>90529</v>
+        <v>78491</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2328,21 +2363,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2352,10 +2387,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>624457</v>
+        <v>624698</v>
       </c>
       <c r="R18" t="n">
-        <v>7298329</v>
+        <v>7298510</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2398,6 +2433,26 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2414,10 +2469,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118937638</v>
+        <v>118941323</v>
       </c>
       <c r="B19" t="n">
-        <v>90529</v>
+        <v>90511</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2430,21 +2485,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2454,10 +2509,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>624563</v>
+        <v>624498</v>
       </c>
       <c r="R19" t="n">
-        <v>7298540</v>
+        <v>7298629</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2516,7 +2571,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118936855</v>
+        <v>118942308</v>
       </c>
       <c r="B20" t="n">
         <v>82270</v>
@@ -2556,10 +2611,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>624670</v>
+        <v>624431</v>
       </c>
       <c r="R20" t="n">
-        <v>7298506</v>
+        <v>7298295</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2602,26 +2657,6 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Picea abies</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2638,7 +2673,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118941819</v>
+        <v>118937638</v>
       </c>
       <c r="B21" t="n">
         <v>90529</v>
@@ -2674,14 +2709,14 @@
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Dalvastjärnen (Dalvastjärnen), Pi lm</t>
+          <t>Balkisberg (Balkisberg), Pi lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>624380</v>
+        <v>624563</v>
       </c>
       <c r="R21" t="n">
-        <v>7298393</v>
+        <v>7298540</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2740,10 +2775,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118936973</v>
+        <v>118941819</v>
       </c>
       <c r="B22" t="n">
-        <v>82270</v>
+        <v>90529</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2756,21 +2791,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1312</v>
+        <v>5432</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2780,10 +2815,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>624645</v>
+        <v>624380</v>
       </c>
       <c r="R22" t="n">
-        <v>7298510</v>
+        <v>7298393</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2842,10 +2877,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>118940936</v>
+        <v>118942245</v>
       </c>
       <c r="B23" t="n">
-        <v>90507</v>
+        <v>78491</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2858,34 +2893,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Balkisberg (Balkisberg), Pi lm</t>
+          <t>Tjakttjure (Tjakttjure), Pi lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>624506</v>
+        <v>624392</v>
       </c>
       <c r="R23" t="n">
-        <v>7298643</v>
+        <v>7298198</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2944,10 +2979,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>118942942</v>
+        <v>118936878</v>
       </c>
       <c r="B24" t="n">
-        <v>82270</v>
+        <v>78491</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2960,21 +2995,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2984,10 +3019,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>624582</v>
+        <v>624645</v>
       </c>
       <c r="R24" t="n">
-        <v>7298506</v>
+        <v>7298514</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3046,10 +3081,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>118938781</v>
+        <v>118939241</v>
       </c>
       <c r="B25" t="n">
-        <v>90954</v>
+        <v>78573</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3058,25 +3093,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1209</v>
+        <v>864</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3089,7 +3124,7 @@
         <v>624606</v>
       </c>
       <c r="R25" t="n">
-        <v>7298573</v>
+        <v>7298605</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3132,26 +3167,6 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
@@ -3168,10 +3183,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>118941803</v>
+        <v>118941656</v>
       </c>
       <c r="B26" t="n">
-        <v>82270</v>
+        <v>90795</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3184,34 +3199,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1312</v>
+        <v>658</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Dalvastjärnen (Dalvastjärnen), Pi lm</t>
+          <t>Balkisberg (Balkisberg), Pi lm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>624381</v>
+        <v>624479</v>
       </c>
       <c r="R26" t="n">
-        <v>7298418</v>
+        <v>7298572</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3270,10 +3285,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>118942069</v>
+        <v>118938882</v>
       </c>
       <c r="B27" t="n">
-        <v>82270</v>
+        <v>90511</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3286,34 +3301,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Tjakttjure (Tjakttjure), Pi lm</t>
+          <t>Balkisberg (Balkisberg), Pi lm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>624287</v>
+        <v>624606</v>
       </c>
       <c r="R27" t="n">
-        <v>7298315</v>
+        <v>7298573</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3372,10 +3387,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>118939884</v>
+        <v>118936855</v>
       </c>
       <c r="B28" t="n">
-        <v>78573</v>
+        <v>82270</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3388,34 +3403,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>864</v>
+        <v>1312</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Balkisberg (Balkisberg), Pi lm</t>
+          <t>Dalvastjärnen (Dalvastjärnen), Pi lm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>624593</v>
+        <v>624670</v>
       </c>
       <c r="R28" t="n">
-        <v>7298603</v>
+        <v>7298506</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3461,12 +3476,12 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>glasbjörk</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
         <is>
-          <t>Betula pubescens</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM28" t="inlineStr">
@@ -3476,7 +3491,7 @@
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Betula pubescens</t>
+          <t>Bark on living woody plant # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3494,10 +3509,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>118938545</v>
+        <v>118938060</v>
       </c>
       <c r="B29" t="n">
-        <v>82270</v>
+        <v>90529</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3510,21 +3525,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1312</v>
+        <v>5432</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3534,10 +3549,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>624578</v>
+        <v>624552</v>
       </c>
       <c r="R29" t="n">
-        <v>7298576</v>
+        <v>7298554</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3596,10 +3611,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>118938454</v>
+        <v>118941737</v>
       </c>
       <c r="B30" t="n">
-        <v>90525</v>
+        <v>78573</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3612,34 +3627,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1204</v>
+        <v>864</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Balkisberg (Balkisberg), Pi lm</t>
+          <t>Badtsavárrie (Badtsavárrie), Pi lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>624580</v>
+        <v>624401</v>
       </c>
       <c r="R30" t="n">
-        <v>7298577</v>
+        <v>7298508</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3698,10 +3713,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>118942330</v>
+        <v>118942598</v>
       </c>
       <c r="B31" t="n">
-        <v>79608</v>
+        <v>90795</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3710,25 +3725,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6464</v>
+        <v>658</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3738,10 +3753,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>624458</v>
+        <v>624471</v>
       </c>
       <c r="R31" t="n">
-        <v>7298303</v>
+        <v>7298339</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3800,10 +3815,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>118942598</v>
+        <v>118941613</v>
       </c>
       <c r="B32" t="n">
-        <v>90795</v>
+        <v>90529</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3816,34 +3831,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Dalvastjärnen (Dalvastjärnen), Pi lm</t>
+          <t>Balkisberg (Balkisberg), Pi lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>624471</v>
+        <v>624497</v>
       </c>
       <c r="R32" t="n">
-        <v>7298339</v>
+        <v>7298652</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3902,10 +3917,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>118942862</v>
+        <v>118941925</v>
       </c>
       <c r="B33" t="n">
-        <v>82270</v>
+        <v>90529</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3918,34 +3933,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1312</v>
+        <v>5432</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Dalvastjärnen (Dalvastjärnen), Pi lm</t>
+          <t>Badtsavárrie (Badtsavárrie), Pi lm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>624490</v>
+        <v>624307</v>
       </c>
       <c r="R33" t="n">
-        <v>7298470</v>
+        <v>7298333</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4004,10 +4019,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>118941751</v>
+        <v>118941943</v>
       </c>
       <c r="B34" t="n">
-        <v>90525</v>
+        <v>90507</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4020,21 +4035,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1204</v>
+        <v>1108</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4044,10 +4059,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>624391</v>
+        <v>624292</v>
       </c>
       <c r="R34" t="n">
-        <v>7298510</v>
+        <v>7298339</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4106,10 +4121,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>118942590</v>
+        <v>118942942</v>
       </c>
       <c r="B35" t="n">
-        <v>90865</v>
+        <v>82270</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4118,38 +4133,38 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1506</v>
+        <v>1312</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Dalvastjärnen (Dalvastjärnen), Pi lm</t>
+          <t>Balkisberg (Balkisberg), Pi lm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>624471</v>
+        <v>624582</v>
       </c>
       <c r="R35" t="n">
-        <v>7298339</v>
+        <v>7298506</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4208,10 +4223,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>118942230</v>
+        <v>118937317</v>
       </c>
       <c r="B36" t="n">
-        <v>90511</v>
+        <v>57290</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4224,34 +4239,39 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Dalvastjärnen (Dalvastjärnen), Pi lm</t>
+          <t>Balkisberg (Balkisberg), Pi lm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>624391</v>
+        <v>624629</v>
       </c>
       <c r="R36" t="n">
-        <v>7298231</v>
+        <v>7298517</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4310,10 +4330,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>118942181</v>
+        <v>118941669</v>
       </c>
       <c r="B37" t="n">
-        <v>90906</v>
+        <v>90507</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4322,38 +4342,38 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4217</v>
+        <v>1108</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Dalvastjärnen (Dalvastjärnen), Pi lm</t>
+          <t>Balkisberg (Balkisberg), Pi lm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>624369</v>
+        <v>624459</v>
       </c>
       <c r="R37" t="n">
-        <v>7298268</v>
+        <v>7298537</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4396,26 +4416,6 @@
       </c>
       <c r="AG37" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ37" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK37" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO37" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
@@ -4432,10 +4432,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>118940575</v>
+        <v>118936785</v>
       </c>
       <c r="B38" t="n">
-        <v>78491</v>
+        <v>78573</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4448,34 +4448,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Balkisberg (Balkisberg), Pi lm</t>
+          <t>Dalvastjärnen (Dalvastjärnen), Pi lm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>624545</v>
+        <v>624687</v>
       </c>
       <c r="R38" t="n">
-        <v>7298672</v>
+        <v>7298499</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4518,6 +4518,26 @@
       </c>
       <c r="AG38" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM38" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Picea abies</t>
+        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
@@ -4534,10 +4554,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>118941925</v>
+        <v>118940936</v>
       </c>
       <c r="B39" t="n">
-        <v>90529</v>
+        <v>90507</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4550,34 +4570,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Badtsavárrie (Badtsavárrie), Pi lm</t>
+          <t>Balkisberg (Balkisberg), Pi lm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>624307</v>
+        <v>624506</v>
       </c>
       <c r="R39" t="n">
-        <v>7298333</v>
+        <v>7298643</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4636,10 +4656,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>118941605</v>
+        <v>118942069</v>
       </c>
       <c r="B40" t="n">
-        <v>90865</v>
+        <v>82270</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4648,38 +4668,38 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1506</v>
+        <v>1312</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Balkisberg (Balkisberg), Pi lm</t>
+          <t>Tjakttjure (Tjakttjure), Pi lm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>624497</v>
+        <v>624287</v>
       </c>
       <c r="R40" t="n">
-        <v>7298652</v>
+        <v>7298315</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4722,26 +4742,6 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ40" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK40" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO40" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
@@ -4758,10 +4758,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>118941943</v>
+        <v>118941605</v>
       </c>
       <c r="B41" t="n">
-        <v>90507</v>
+        <v>90865</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4770,38 +4770,38 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1108</v>
+        <v>1506</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Badtsavárrie (Badtsavárrie), Pi lm</t>
+          <t>Balkisberg (Balkisberg), Pi lm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>624292</v>
+        <v>624497</v>
       </c>
       <c r="R41" t="n">
-        <v>7298339</v>
+        <v>7298652</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4844,6 +4844,26 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM41" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
@@ -4860,10 +4880,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>118936726</v>
+        <v>118942762</v>
       </c>
       <c r="B42" t="n">
-        <v>78491</v>
+        <v>90529</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4876,21 +4896,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4900,10 +4920,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>624698</v>
+        <v>624452</v>
       </c>
       <c r="R42" t="n">
-        <v>7298510</v>
+        <v>7298419</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4946,26 +4966,6 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ42" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK42" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO42" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
@@ -4982,10 +4982,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>118941713</v>
+        <v>118939884</v>
       </c>
       <c r="B43" t="n">
-        <v>78491</v>
+        <v>78573</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4998,21 +4998,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5022,10 +5022,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>624408</v>
+        <v>624593</v>
       </c>
       <c r="R43" t="n">
-        <v>7298513</v>
+        <v>7298603</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5068,6 +5068,26 @@
       </c>
       <c r="AG43" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>glasbjörk</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>Betula pubescens</t>
+        </is>
+      </c>
+      <c r="AM43" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Betula pubescens</t>
+        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
@@ -5084,10 +5104,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>118941656</v>
+        <v>118942910</v>
       </c>
       <c r="B44" t="n">
-        <v>90795</v>
+        <v>78491</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5100,21 +5120,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5124,10 +5144,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>624479</v>
+        <v>624550</v>
       </c>
       <c r="R44" t="n">
-        <v>7298572</v>
+        <v>7298507</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5186,10 +5206,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>118941669</v>
+        <v>118941838</v>
       </c>
       <c r="B45" t="n">
-        <v>90507</v>
+        <v>79573</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5202,34 +5222,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1108</v>
+        <v>2081</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Balkisberg (Balkisberg), Pi lm</t>
+          <t>Dalvastjärnen (Dalvastjärnen), Pi lm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>624459</v>
+        <v>624377</v>
       </c>
       <c r="R45" t="n">
-        <v>7298537</v>
+        <v>7298392</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5272,6 +5292,26 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM45" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
@@ -5288,10 +5328,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>118942067</v>
+        <v>118941779</v>
       </c>
       <c r="B46" t="n">
-        <v>78491</v>
+        <v>90954</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5300,38 +5340,38 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Tjakttjure (Tjakttjure), Pi lm</t>
+          <t>Badtsavárrie (Badtsavárrie), Pi lm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>624287</v>
+        <v>624395</v>
       </c>
       <c r="R46" t="n">
-        <v>7298315</v>
+        <v>7298485</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5390,10 +5430,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>118941785</v>
+        <v>118936973</v>
       </c>
       <c r="B47" t="n">
-        <v>90795</v>
+        <v>82270</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5406,34 +5446,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>658</v>
+        <v>1312</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Badtsavárrie (Badtsavárrie), Pi lm</t>
+          <t>Dalvastjärnen (Dalvastjärnen), Pi lm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>624395</v>
+        <v>624645</v>
       </c>
       <c r="R47" t="n">
-        <v>7298485</v>
+        <v>7298510</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5492,10 +5532,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>118942784</v>
+        <v>118942230</v>
       </c>
       <c r="B48" t="n">
-        <v>78491</v>
+        <v>90511</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5508,21 +5548,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5532,10 +5572,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>624426</v>
+        <v>624391</v>
       </c>
       <c r="R48" t="n">
-        <v>7298414</v>
+        <v>7298231</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5594,10 +5634,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>118938882</v>
+        <v>118942381</v>
       </c>
       <c r="B49" t="n">
-        <v>90511</v>
+        <v>90795</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5610,34 +5650,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Balkisberg (Balkisberg), Pi lm</t>
+          <t>Dalvastjärnen (Dalvastjärnen), Pi lm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>624606</v>
+        <v>624423</v>
       </c>
       <c r="R49" t="n">
-        <v>7298573</v>
+        <v>7298332</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5696,10 +5736,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>118936785</v>
+        <v>118941845</v>
       </c>
       <c r="B50" t="n">
-        <v>78573</v>
+        <v>79608</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5708,25 +5748,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>864</v>
+        <v>6464</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5736,10 +5776,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>624687</v>
+        <v>624377</v>
       </c>
       <c r="R50" t="n">
-        <v>7298499</v>
+        <v>7298392</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5782,26 +5822,6 @@
       </c>
       <c r="AG50" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ50" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK50" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM50" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO50" t="inlineStr">
-        <is>
-          <t>Bark of dead wood # Picea abies</t>
-        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
@@ -5818,7 +5838,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>118942910</v>
+        <v>118940575</v>
       </c>
       <c r="B51" t="n">
         <v>78491</v>
@@ -5858,10 +5878,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>624550</v>
+        <v>624545</v>
       </c>
       <c r="R51" t="n">
-        <v>7298507</v>
+        <v>7298672</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5920,10 +5940,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>118941737</v>
+        <v>118941803</v>
       </c>
       <c r="B52" t="n">
-        <v>78573</v>
+        <v>82270</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5936,34 +5956,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>864</v>
+        <v>1312</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Badtsavárrie (Badtsavárrie), Pi lm</t>
+          <t>Dalvastjärnen (Dalvastjärnen), Pi lm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>624401</v>
+        <v>624381</v>
       </c>
       <c r="R52" t="n">
-        <v>7298508</v>
+        <v>7298418</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6022,10 +6042,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>118941838</v>
+        <v>118941751</v>
       </c>
       <c r="B53" t="n">
-        <v>79573</v>
+        <v>90525</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6038,34 +6058,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>2081</v>
+        <v>1204</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Dalvastjärnen (Dalvastjärnen), Pi lm</t>
+          <t>Badtsavárrie (Badtsavárrie), Pi lm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>624377</v>
+        <v>624391</v>
       </c>
       <c r="R53" t="n">
-        <v>7298392</v>
+        <v>7298510</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6108,26 +6128,6 @@
       </c>
       <c r="AG53" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ53" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK53" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM53" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO53" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">

--- a/artfynd/A 64805-2023 artfynd.xlsx
+++ b/artfynd/A 64805-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY53"/>
+  <dimension ref="A1:AY46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118942245</v>
+        <v>118938830</v>
       </c>
       <c r="B2" t="n">
-        <v>78493</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,34 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Tjakttjure (Tjakttjure), Pi lm</t>
+          <t>Balkisberg, Balkisberg, Pi lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>624392</v>
+        <v>624606</v>
       </c>
       <c r="R2" t="n">
-        <v>7298198</v>
+        <v>7298573</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118942910</v>
+        <v>118941656</v>
       </c>
       <c r="B3" t="n">
-        <v>78493</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,34 +783,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Balkisberg (Balkisberg), Pi lm</t>
+          <t>Balkisberg, Balkisberg, Pi lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>624550</v>
+        <v>624479</v>
       </c>
       <c r="R3" t="n">
-        <v>7298507</v>
+        <v>7298572</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,15 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118938454</v>
+        <v>118941785</v>
       </c>
       <c r="B4" t="n">
-        <v>90527</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -895,34 +880,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1204</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Balkisberg (Balkisberg), Pi lm</t>
+          <t>Badtsavárrie, Badtsavárrie, Pi lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>624580</v>
+        <v>624395</v>
       </c>
       <c r="R4" t="n">
-        <v>7298577</v>
+        <v>7298485</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,15 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118941737</v>
+        <v>118942381</v>
       </c>
       <c r="B5" t="n">
-        <v>78575</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -997,34 +977,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>864</v>
+        <v>658</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Badtsavárrie (Badtsavárrie), Pi lm</t>
+          <t>Dalvastjärnen, Dalvastjärnen, Pi lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>624401</v>
+        <v>624423</v>
       </c>
       <c r="R5" t="n">
-        <v>7298508</v>
+        <v>7298332</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,15 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118940084</v>
+        <v>118942598</v>
       </c>
       <c r="B6" t="n">
-        <v>90509</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1099,34 +1074,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1108</v>
+        <v>658</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Balkisberg (Balkisberg), Pi lm</t>
+          <t>Dalvastjärnen, Dalvastjärnen, Pi lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>624586</v>
+        <v>624471</v>
       </c>
       <c r="R6" t="n">
-        <v>7298607</v>
+        <v>7298339</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,15 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118941713</v>
+        <v>118936785</v>
       </c>
       <c r="B7" t="n">
-        <v>78493</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1201,34 +1171,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Balkisberg (Balkisberg), Pi lm</t>
+          <t>Dalvastjärnen, Dalvastjärnen, Pi lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>624408</v>
+        <v>624687</v>
       </c>
       <c r="R7" t="n">
-        <v>7298513</v>
+        <v>7298499</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1271,6 +1241,26 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Picea abies</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1287,15 +1277,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118936785</v>
+        <v>118939241</v>
       </c>
       <c r="B8" t="n">
-        <v>78575</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1323,14 +1308,14 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Dalvastjärnen (Dalvastjärnen), Pi lm</t>
+          <t>Balkisberg, Balkisberg, Pi lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>624687</v>
+        <v>624606</v>
       </c>
       <c r="R8" t="n">
-        <v>7298499</v>
+        <v>7298605</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1373,26 +1358,6 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Bark of dead wood # Picea abies</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1412,12 +1377,7 @@
         <v>118939884</v>
       </c>
       <c r="B9" t="n">
-        <v>78575</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1445,7 +1405,7 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Balkisberg (Balkisberg), Pi lm</t>
+          <t>Balkisberg, Balkisberg, Pi lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
@@ -1531,15 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118941925</v>
+        <v>118941737</v>
       </c>
       <c r="B10" t="n">
-        <v>90531</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1547,34 +1502,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>864</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Badtsavárrie (Badtsavárrie), Pi lm</t>
+          <t>Badtsavárrie, Badtsavárrie, Pi lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>624307</v>
+        <v>624401</v>
       </c>
       <c r="R10" t="n">
-        <v>7298333</v>
+        <v>7298508</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1633,15 +1588,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118942762</v>
+        <v>118940084</v>
       </c>
       <c r="B11" t="n">
-        <v>90531</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1649,34 +1599,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Dalvastjärnen (Dalvastjärnen), Pi lm</t>
+          <t>Balkisberg, Balkisberg, Pi lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>624452</v>
+        <v>624586</v>
       </c>
       <c r="R11" t="n">
-        <v>7298419</v>
+        <v>7298607</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1735,15 +1685,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118941819</v>
+        <v>118940936</v>
       </c>
       <c r="B12" t="n">
-        <v>90531</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1751,34 +1696,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Dalvastjärnen (Dalvastjärnen), Pi lm</t>
+          <t>Balkisberg, Balkisberg, Pi lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>624380</v>
+        <v>624506</v>
       </c>
       <c r="R12" t="n">
-        <v>7298393</v>
+        <v>7298643</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1837,15 +1782,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118936726</v>
+        <v>118941669</v>
       </c>
       <c r="B13" t="n">
-        <v>78493</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1853,34 +1793,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Dalvastjärnen (Dalvastjärnen), Pi lm</t>
+          <t>Balkisberg, Balkisberg, Pi lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>624698</v>
+        <v>624459</v>
       </c>
       <c r="R13" t="n">
-        <v>7298510</v>
+        <v>7298537</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1923,26 +1863,6 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -1959,15 +1879,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118936878</v>
+        <v>118941943</v>
       </c>
       <c r="B14" t="n">
-        <v>78493</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1975,34 +1890,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Balkisberg (Balkisberg), Pi lm</t>
+          <t>Badtsavárrie, Badtsavárrie, Pi lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>624645</v>
+        <v>624292</v>
       </c>
       <c r="R14" t="n">
-        <v>7298514</v>
+        <v>7298339</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2061,15 +1976,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118937638</v>
+        <v>118936910</v>
       </c>
       <c r="B15" t="n">
-        <v>90531</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2077,34 +1987,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Balkisberg (Balkisberg), Pi lm</t>
+          <t>Balkisberg, Balkisberg, Pi lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>624563</v>
+        <v>624659</v>
       </c>
       <c r="R15" t="n">
-        <v>7298540</v>
+        <v>7298524</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2163,15 +2073,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118942480</v>
+        <v>118938882</v>
       </c>
       <c r="B16" t="n">
-        <v>90531</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2179,34 +2084,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Dalvastjärnen (Dalvastjärnen), Pi lm</t>
+          <t>Balkisberg, Balkisberg, Pi lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>624457</v>
+        <v>624606</v>
       </c>
       <c r="R16" t="n">
-        <v>7298329</v>
+        <v>7298573</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2265,15 +2170,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118942862</v>
+        <v>118941323</v>
       </c>
       <c r="B17" t="n">
-        <v>82272</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2281,34 +2181,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Dalvastjärnen (Dalvastjärnen), Pi lm</t>
+          <t>Balkisberg, Balkisberg, Pi lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>624490</v>
+        <v>624498</v>
       </c>
       <c r="R17" t="n">
-        <v>7298470</v>
+        <v>7298629</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2367,50 +2267,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118942590</v>
+        <v>118942230</v>
       </c>
       <c r="B18" t="n">
-        <v>90867</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1506</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Dalvastjärnen (Dalvastjärnen), Pi lm</t>
+          <t>Dalvastjärnen, Dalvastjärnen, Pi lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>624471</v>
+        <v>624391</v>
       </c>
       <c r="R18" t="n">
-        <v>7298339</v>
+        <v>7298231</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2469,50 +2364,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118941669</v>
+        <v>118938454</v>
       </c>
       <c r="B19" t="n">
-        <v>90509</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1108</v>
+        <v>1204</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Balkisberg (Balkisberg), Pi lm</t>
+          <t>Balkisberg, Balkisberg, Pi lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>624459</v>
+        <v>624580</v>
       </c>
       <c r="R19" t="n">
-        <v>7298537</v>
+        <v>7298577</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2571,50 +2461,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118936910</v>
+        <v>118941751</v>
       </c>
       <c r="B20" t="n">
-        <v>90513</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Balkisberg (Balkisberg), Pi lm</t>
+          <t>Badtsavárrie, Badtsavárrie, Pi lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>624659</v>
+        <v>624391</v>
       </c>
       <c r="R20" t="n">
-        <v>7298524</v>
+        <v>7298510</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2673,15 +2558,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118936973</v>
+        <v>118938781</v>
       </c>
       <c r="B21" t="n">
-        <v>82272</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2689,34 +2569,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1312</v>
+        <v>1209</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Dalvastjärnen (Dalvastjärnen), Pi lm</t>
+          <t>Balkisberg, Balkisberg, Pi lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>624645</v>
+        <v>624606</v>
       </c>
       <c r="R21" t="n">
-        <v>7298510</v>
+        <v>7298573</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2759,6 +2639,26 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -2775,19 +2675,14 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118938781</v>
+        <v>118941779</v>
       </c>
       <c r="B22" t="n">
-        <v>90956</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
@@ -2800,25 +2695,25 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Balkisberg (Balkisberg), Pi lm</t>
+          <t>Badtsavárrie, Badtsavárrie, Pi lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>624606</v>
+        <v>624395</v>
       </c>
       <c r="R22" t="n">
-        <v>7298573</v>
+        <v>7298485</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2861,26 +2756,6 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -2897,50 +2772,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>118942330</v>
+        <v>118936855</v>
       </c>
       <c r="B23" t="n">
-        <v>79610</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6464</v>
+        <v>1312</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Dalvastjärnen (Dalvastjärnen), Pi lm</t>
+          <t>Dalvastjärnen, Dalvastjärnen, Pi lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>624458</v>
+        <v>624670</v>
       </c>
       <c r="R23" t="n">
-        <v>7298303</v>
+        <v>7298506</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2983,6 +2853,26 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Picea abies</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -2999,15 +2889,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>118937317</v>
+        <v>118936973</v>
       </c>
       <c r="B24" t="n">
-        <v>57292</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3015,39 +2900,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Balkisberg (Balkisberg), Pi lm</t>
+          <t>Dalvastjärnen, Dalvastjärnen, Pi lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>624629</v>
+        <v>624645</v>
       </c>
       <c r="R24" t="n">
-        <v>7298517</v>
+        <v>7298510</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3106,15 +2986,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>118942598</v>
+        <v>118938545</v>
       </c>
       <c r="B25" t="n">
-        <v>90797</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3122,34 +2997,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>658</v>
+        <v>1312</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Dalvastjärnen (Dalvastjärnen), Pi lm</t>
+          <t>Balkisberg, Balkisberg, Pi lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>624471</v>
+        <v>624578</v>
       </c>
       <c r="R25" t="n">
-        <v>7298339</v>
+        <v>7298576</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3208,15 +3083,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>118941785</v>
+        <v>118941803</v>
       </c>
       <c r="B26" t="n">
-        <v>90797</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3224,34 +3094,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>658</v>
+        <v>1312</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Badtsavárrie (Badtsavárrie), Pi lm</t>
+          <t>Dalvastjärnen, Dalvastjärnen, Pi lm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>624395</v>
+        <v>624381</v>
       </c>
       <c r="R26" t="n">
-        <v>7298485</v>
+        <v>7298418</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3310,15 +3180,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>118940575</v>
+        <v>118942069</v>
       </c>
       <c r="B27" t="n">
-        <v>78493</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3326,34 +3191,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Balkisberg (Balkisberg), Pi lm</t>
+          <t>Tjakttjure, Tjakttjure, Pi lm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>624545</v>
+        <v>624287</v>
       </c>
       <c r="R27" t="n">
-        <v>7298672</v>
+        <v>7298315</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3412,50 +3277,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>118942694</v>
+        <v>118942308</v>
       </c>
       <c r="B28" t="n">
-        <v>90478</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5447</v>
+        <v>1312</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Dalvastjärnen (Dalvastjärnen), Pi lm</t>
+          <t>Dalvastjärnen, Dalvastjärnen, Pi lm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>624468</v>
+        <v>624431</v>
       </c>
       <c r="R28" t="n">
-        <v>7298362</v>
+        <v>7298295</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3514,15 +3374,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>118938060</v>
+        <v>118942862</v>
       </c>
       <c r="B29" t="n">
-        <v>90531</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3530,34 +3385,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Balkisberg (Balkisberg), Pi lm</t>
+          <t>Dalvastjärnen, Dalvastjärnen, Pi lm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>624552</v>
+        <v>624490</v>
       </c>
       <c r="R29" t="n">
-        <v>7298554</v>
+        <v>7298470</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3616,15 +3471,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>118938545</v>
+        <v>118942942</v>
       </c>
       <c r="B30" t="n">
-        <v>82272</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3652,14 +3502,14 @@
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Balkisberg (Balkisberg), Pi lm</t>
+          <t>Balkisberg, Balkisberg, Pi lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>624578</v>
+        <v>624582</v>
       </c>
       <c r="R30" t="n">
-        <v>7298576</v>
+        <v>7298506</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3718,50 +3568,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>118942381</v>
+        <v>118941605</v>
       </c>
       <c r="B31" t="n">
-        <v>90797</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92292</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>658</v>
+        <v>1506</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Dalvastjärnen (Dalvastjärnen), Pi lm</t>
+          <t>Balkisberg, Balkisberg, Pi lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>624423</v>
+        <v>624497</v>
       </c>
       <c r="R31" t="n">
-        <v>7298332</v>
+        <v>7298652</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3804,6 +3649,26 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM31" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
@@ -3820,50 +3685,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>118940936</v>
+        <v>118942590</v>
       </c>
       <c r="B32" t="n">
-        <v>90509</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92292</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1108</v>
+        <v>1506</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Balkisberg (Balkisberg), Pi lm</t>
+          <t>Dalvastjärnen, Dalvastjärnen, Pi lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>624506</v>
+        <v>624471</v>
       </c>
       <c r="R32" t="n">
-        <v>7298643</v>
+        <v>7298339</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3922,15 +3782,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>118938882</v>
+        <v>118941838</v>
       </c>
       <c r="B33" t="n">
-        <v>90513</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3938,34 +3793,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Balkisberg (Balkisberg), Pi lm</t>
+          <t>Dalvastjärnen, Dalvastjärnen, Pi lm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>624606</v>
+        <v>624377</v>
       </c>
       <c r="R33" t="n">
-        <v>7298573</v>
+        <v>7298392</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4008,6 +3863,26 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM33" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
@@ -4024,50 +3899,45 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>118941779</v>
+        <v>118942181</v>
       </c>
       <c r="B34" t="n">
-        <v>90956</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92333</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1209</v>
+        <v>4217</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Badtsavárrie (Badtsavárrie), Pi lm</t>
+          <t>Dalvastjärnen, Dalvastjärnen, Pi lm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>624395</v>
+        <v>624369</v>
       </c>
       <c r="R34" t="n">
-        <v>7298485</v>
+        <v>7298268</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4110,6 +3980,26 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM34" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
@@ -4126,50 +4016,45 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>118942230</v>
+        <v>118942694</v>
       </c>
       <c r="B35" t="n">
-        <v>90513</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Dalvastjärnen (Dalvastjärnen), Pi lm</t>
+          <t>Dalvastjärnen, Dalvastjärnen, Pi lm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>624391</v>
+        <v>624468</v>
       </c>
       <c r="R35" t="n">
-        <v>7298231</v>
+        <v>7298362</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4228,50 +4113,45 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>118941613</v>
+        <v>118936726</v>
       </c>
       <c r="B36" t="n">
-        <v>90531</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Balkisberg (Balkisberg), Pi lm</t>
+          <t>Dalvastjärnen, Dalvastjärnen, Pi lm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>624497</v>
+        <v>624698</v>
       </c>
       <c r="R36" t="n">
-        <v>7298652</v>
+        <v>7298510</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4314,6 +4194,26 @@
       </c>
       <c r="AG36" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM36" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
@@ -4330,50 +4230,45 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>118941845</v>
+        <v>118936878</v>
       </c>
       <c r="B37" t="n">
-        <v>79610</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Dalvastjärnen (Dalvastjärnen), Pi lm</t>
+          <t>Balkisberg, Balkisberg, Pi lm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>624377</v>
+        <v>624645</v>
       </c>
       <c r="R37" t="n">
-        <v>7298392</v>
+        <v>7298514</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4432,50 +4327,45 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>118941838</v>
+        <v>118940575</v>
       </c>
       <c r="B38" t="n">
-        <v>79575</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Dalvastjärnen (Dalvastjärnen), Pi lm</t>
+          <t>Balkisberg, Balkisberg, Pi lm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>624377</v>
+        <v>624545</v>
       </c>
       <c r="R38" t="n">
-        <v>7298392</v>
+        <v>7298672</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4518,26 +4408,6 @@
       </c>
       <c r="AG38" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ38" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK38" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO38" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
@@ -4554,50 +4424,45 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>118942181</v>
+        <v>118941713</v>
       </c>
       <c r="B39" t="n">
-        <v>90908</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4217</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Dalvastjärnen (Dalvastjärnen), Pi lm</t>
+          <t>Balkisberg, Balkisberg, Pi lm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>624369</v>
+        <v>624408</v>
       </c>
       <c r="R39" t="n">
-        <v>7298268</v>
+        <v>7298513</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4640,26 +4505,6 @@
       </c>
       <c r="AG39" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ39" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK39" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO39" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
@@ -4676,50 +4521,45 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>118942308</v>
+        <v>118942067</v>
       </c>
       <c r="B40" t="n">
-        <v>82272</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Dalvastjärnen (Dalvastjärnen), Pi lm</t>
+          <t>Tjakttjure, Tjakttjure, Pi lm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>624431</v>
+        <v>624287</v>
       </c>
       <c r="R40" t="n">
-        <v>7298295</v>
+        <v>7298315</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4778,50 +4618,45 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>118941656</v>
+        <v>118942245</v>
       </c>
       <c r="B41" t="n">
-        <v>90797</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Balkisberg (Balkisberg), Pi lm</t>
+          <t>Tjakttjure, Tjakttjure, Pi lm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>624479</v>
+        <v>624392</v>
       </c>
       <c r="R41" t="n">
-        <v>7298572</v>
+        <v>7298198</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4880,50 +4715,45 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>118941751</v>
+        <v>118942784</v>
       </c>
       <c r="B42" t="n">
-        <v>90527</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Badtsavárrie (Badtsavárrie), Pi lm</t>
+          <t>Dalvastjärnen, Dalvastjärnen, Pi lm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>624391</v>
+        <v>624426</v>
       </c>
       <c r="R42" t="n">
-        <v>7298510</v>
+        <v>7298414</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4982,50 +4812,45 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>118942069</v>
+        <v>118942910</v>
       </c>
       <c r="B43" t="n">
-        <v>82272</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Tjakttjure (Tjakttjure), Pi lm</t>
+          <t>Balkisberg, Balkisberg, Pi lm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>624287</v>
+        <v>624550</v>
       </c>
       <c r="R43" t="n">
-        <v>7298315</v>
+        <v>7298507</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5084,50 +4909,45 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>118942067</v>
+        <v>118941845</v>
       </c>
       <c r="B44" t="n">
-        <v>78493</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80468</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Tjakttjure (Tjakttjure), Pi lm</t>
+          <t>Dalvastjärnen, Dalvastjärnen, Pi lm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>624287</v>
+        <v>624377</v>
       </c>
       <c r="R44" t="n">
-        <v>7298315</v>
+        <v>7298392</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5186,50 +5006,45 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>118939241</v>
+        <v>118942330</v>
       </c>
       <c r="B45" t="n">
-        <v>78575</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80468</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>864</v>
+        <v>6464</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Balkisberg (Balkisberg), Pi lm</t>
+          <t>Dalvastjärnen, Dalvastjärnen, Pi lm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>624606</v>
+        <v>624458</v>
       </c>
       <c r="R45" t="n">
-        <v>7298605</v>
+        <v>7298303</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5288,15 +5103,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>118941803</v>
+        <v>118937317</v>
       </c>
       <c r="B46" t="n">
-        <v>82272</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5304,34 +5114,39 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Dalvastjärnen (Dalvastjärnen), Pi lm</t>
+          <t>Balkisberg, Balkisberg, Pi lm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>624381</v>
+        <v>624629</v>
       </c>
       <c r="R46" t="n">
-        <v>7298418</v>
+        <v>7298517</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5387,760 +5202,6 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" t="n">
-        <v>118941605</v>
-      </c>
-      <c r="B47" t="n">
-        <v>90867</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E47" t="n">
-        <v>1506</v>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>Ostticka</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>Skeletocutis odora</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>(Sacc.) Ginns</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
-      <c r="P47" t="inlineStr">
-        <is>
-          <t>Balkisberg (Balkisberg), Pi lm</t>
-        </is>
-      </c>
-      <c r="Q47" t="n">
-        <v>624497</v>
-      </c>
-      <c r="R47" t="n">
-        <v>7298652</v>
-      </c>
-      <c r="S47" t="n">
-        <v>10</v>
-      </c>
-      <c r="T47" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U47" t="inlineStr">
-        <is>
-          <t>Arjeplog</t>
-        </is>
-      </c>
-      <c r="V47" t="inlineStr">
-        <is>
-          <t>Pite lappmark</t>
-        </is>
-      </c>
-      <c r="W47" t="inlineStr">
-        <is>
-          <t>Arjeplog</t>
-        </is>
-      </c>
-      <c r="Y47" t="inlineStr">
-        <is>
-          <t>2024-08-05</t>
-        </is>
-      </c>
-      <c r="AA47" t="inlineStr">
-        <is>
-          <t>2024-08-05</t>
-        </is>
-      </c>
-      <c r="AD47" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE47" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG47" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ47" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK47" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM47" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO47" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
-        </is>
-      </c>
-      <c r="AT47" t="inlineStr"/>
-      <c r="AW47" t="inlineStr">
-        <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AX47" t="inlineStr">
-        <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY47" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" t="n">
-        <v>118942942</v>
-      </c>
-      <c r="B48" t="n">
-        <v>82272</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E48" t="n">
-        <v>1312</v>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>Gammelgransskål</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>Pseudographis pinicola</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
-      <c r="P48" t="inlineStr">
-        <is>
-          <t>Balkisberg (Balkisberg), Pi lm</t>
-        </is>
-      </c>
-      <c r="Q48" t="n">
-        <v>624582</v>
-      </c>
-      <c r="R48" t="n">
-        <v>7298506</v>
-      </c>
-      <c r="S48" t="n">
-        <v>10</v>
-      </c>
-      <c r="T48" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U48" t="inlineStr">
-        <is>
-          <t>Arjeplog</t>
-        </is>
-      </c>
-      <c r="V48" t="inlineStr">
-        <is>
-          <t>Pite lappmark</t>
-        </is>
-      </c>
-      <c r="W48" t="inlineStr">
-        <is>
-          <t>Arjeplog</t>
-        </is>
-      </c>
-      <c r="Y48" t="inlineStr">
-        <is>
-          <t>2024-08-05</t>
-        </is>
-      </c>
-      <c r="AA48" t="inlineStr">
-        <is>
-          <t>2024-08-05</t>
-        </is>
-      </c>
-      <c r="AD48" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE48" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG48" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT48" t="inlineStr"/>
-      <c r="AW48" t="inlineStr">
-        <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AX48" t="inlineStr">
-        <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY48" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" t="n">
-        <v>118938830</v>
-      </c>
-      <c r="B49" t="n">
-        <v>90797</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E49" t="n">
-        <v>658</v>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>Rosenticka</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>Rhodofomes roseus</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
-      <c r="P49" t="inlineStr">
-        <is>
-          <t>Balkisberg (Balkisberg), Pi lm</t>
-        </is>
-      </c>
-      <c r="Q49" t="n">
-        <v>624606</v>
-      </c>
-      <c r="R49" t="n">
-        <v>7298573</v>
-      </c>
-      <c r="S49" t="n">
-        <v>10</v>
-      </c>
-      <c r="T49" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U49" t="inlineStr">
-        <is>
-          <t>Arjeplog</t>
-        </is>
-      </c>
-      <c r="V49" t="inlineStr">
-        <is>
-          <t>Pite lappmark</t>
-        </is>
-      </c>
-      <c r="W49" t="inlineStr">
-        <is>
-          <t>Arjeplog</t>
-        </is>
-      </c>
-      <c r="Y49" t="inlineStr">
-        <is>
-          <t>2024-08-05</t>
-        </is>
-      </c>
-      <c r="AA49" t="inlineStr">
-        <is>
-          <t>2024-08-05</t>
-        </is>
-      </c>
-      <c r="AD49" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE49" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG49" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT49" t="inlineStr"/>
-      <c r="AW49" t="inlineStr">
-        <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AX49" t="inlineStr">
-        <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY49" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" t="n">
-        <v>118942784</v>
-      </c>
-      <c r="B50" t="n">
-        <v>78493</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E50" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
-      <c r="P50" t="inlineStr">
-        <is>
-          <t>Dalvastjärnen (Dalvastjärnen), Pi lm</t>
-        </is>
-      </c>
-      <c r="Q50" t="n">
-        <v>624426</v>
-      </c>
-      <c r="R50" t="n">
-        <v>7298414</v>
-      </c>
-      <c r="S50" t="n">
-        <v>10</v>
-      </c>
-      <c r="T50" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U50" t="inlineStr">
-        <is>
-          <t>Arjeplog</t>
-        </is>
-      </c>
-      <c r="V50" t="inlineStr">
-        <is>
-          <t>Pite lappmark</t>
-        </is>
-      </c>
-      <c r="W50" t="inlineStr">
-        <is>
-          <t>Arjeplog</t>
-        </is>
-      </c>
-      <c r="Y50" t="inlineStr">
-        <is>
-          <t>2024-08-05</t>
-        </is>
-      </c>
-      <c r="AA50" t="inlineStr">
-        <is>
-          <t>2024-08-05</t>
-        </is>
-      </c>
-      <c r="AD50" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE50" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG50" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT50" t="inlineStr"/>
-      <c r="AW50" t="inlineStr">
-        <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AX50" t="inlineStr">
-        <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY50" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" t="n">
-        <v>118941943</v>
-      </c>
-      <c r="B51" t="n">
-        <v>90509</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E51" t="n">
-        <v>1108</v>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>Harticka</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>Pelloporus leporinus</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
-      <c r="P51" t="inlineStr">
-        <is>
-          <t>Badtsavárrie (Badtsavárrie), Pi lm</t>
-        </is>
-      </c>
-      <c r="Q51" t="n">
-        <v>624292</v>
-      </c>
-      <c r="R51" t="n">
-        <v>7298339</v>
-      </c>
-      <c r="S51" t="n">
-        <v>10</v>
-      </c>
-      <c r="T51" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U51" t="inlineStr">
-        <is>
-          <t>Arjeplog</t>
-        </is>
-      </c>
-      <c r="V51" t="inlineStr">
-        <is>
-          <t>Pite lappmark</t>
-        </is>
-      </c>
-      <c r="W51" t="inlineStr">
-        <is>
-          <t>Arjeplog</t>
-        </is>
-      </c>
-      <c r="Y51" t="inlineStr">
-        <is>
-          <t>2024-08-05</t>
-        </is>
-      </c>
-      <c r="AA51" t="inlineStr">
-        <is>
-          <t>2024-08-05</t>
-        </is>
-      </c>
-      <c r="AD51" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE51" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG51" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT51" t="inlineStr"/>
-      <c r="AW51" t="inlineStr">
-        <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AX51" t="inlineStr">
-        <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY51" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" t="n">
-        <v>118936855</v>
-      </c>
-      <c r="B52" t="n">
-        <v>82272</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E52" t="n">
-        <v>1312</v>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>Gammelgransskål</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>Pseudographis pinicola</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
-      <c r="P52" t="inlineStr">
-        <is>
-          <t>Dalvastjärnen (Dalvastjärnen), Pi lm</t>
-        </is>
-      </c>
-      <c r="Q52" t="n">
-        <v>624670</v>
-      </c>
-      <c r="R52" t="n">
-        <v>7298506</v>
-      </c>
-      <c r="S52" t="n">
-        <v>10</v>
-      </c>
-      <c r="T52" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U52" t="inlineStr">
-        <is>
-          <t>Arjeplog</t>
-        </is>
-      </c>
-      <c r="V52" t="inlineStr">
-        <is>
-          <t>Pite lappmark</t>
-        </is>
-      </c>
-      <c r="W52" t="inlineStr">
-        <is>
-          <t>Arjeplog</t>
-        </is>
-      </c>
-      <c r="Y52" t="inlineStr">
-        <is>
-          <t>2024-08-05</t>
-        </is>
-      </c>
-      <c r="AA52" t="inlineStr">
-        <is>
-          <t>2024-08-05</t>
-        </is>
-      </c>
-      <c r="AD52" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE52" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG52" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ52" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK52" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM52" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO52" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Picea abies</t>
-        </is>
-      </c>
-      <c r="AT52" t="inlineStr"/>
-      <c r="AW52" t="inlineStr">
-        <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AX52" t="inlineStr">
-        <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY52" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="A53" t="n">
-        <v>118941323</v>
-      </c>
-      <c r="B53" t="n">
-        <v>90513</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E53" t="n">
-        <v>1202</v>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>Ullticka</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
-      <c r="P53" t="inlineStr">
-        <is>
-          <t>Balkisberg (Balkisberg), Pi lm</t>
-        </is>
-      </c>
-      <c r="Q53" t="n">
-        <v>624498</v>
-      </c>
-      <c r="R53" t="n">
-        <v>7298629</v>
-      </c>
-      <c r="S53" t="n">
-        <v>10</v>
-      </c>
-      <c r="T53" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U53" t="inlineStr">
-        <is>
-          <t>Arjeplog</t>
-        </is>
-      </c>
-      <c r="V53" t="inlineStr">
-        <is>
-          <t>Pite lappmark</t>
-        </is>
-      </c>
-      <c r="W53" t="inlineStr">
-        <is>
-          <t>Arjeplog</t>
-        </is>
-      </c>
-      <c r="Y53" t="inlineStr">
-        <is>
-          <t>2024-08-05</t>
-        </is>
-      </c>
-      <c r="AA53" t="inlineStr">
-        <is>
-          <t>2024-08-05</t>
-        </is>
-      </c>
-      <c r="AD53" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE53" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG53" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT53" t="inlineStr"/>
-      <c r="AW53" t="inlineStr">
-        <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AX53" t="inlineStr">
-        <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY53" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 64805-2023 artfynd.xlsx
+++ b/artfynd/A 64805-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY46"/>
+  <dimension ref="A1:AY56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118938830</v>
+        <v>135330034</v>
       </c>
       <c r="B2" t="n">
-        <v>92208</v>
+        <v>97435</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,37 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>658</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Balkisberg, Balkisberg, Pi lm</t>
+          <t>Balkisberg 260721, Pi lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>624606</v>
+        <v>624594</v>
       </c>
       <c r="R2" t="n">
-        <v>7298573</v>
+        <v>7298492</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -740,12 +740,27 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-08-05</t>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-08-05</t>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Grön röd brun</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -760,19 +775,23 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Katharina Radloff</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>Katharina Radloff</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118941656</v>
+        <v>118938830</v>
       </c>
       <c r="B3" t="n">
         <v>92208</v>
@@ -807,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>624479</v>
+        <v>624606</v>
       </c>
       <c r="R3" t="n">
-        <v>7298572</v>
+        <v>7298573</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,7 +888,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118941785</v>
+        <v>118941656</v>
       </c>
       <c r="B4" t="n">
         <v>92208</v>
@@ -900,14 +919,14 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Badtsavárrie, Badtsavárrie, Pi lm</t>
+          <t>Balkisberg, Balkisberg, Pi lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>624395</v>
+        <v>624479</v>
       </c>
       <c r="R4" t="n">
-        <v>7298485</v>
+        <v>7298572</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,7 +985,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118942381</v>
+        <v>118941785</v>
       </c>
       <c r="B5" t="n">
         <v>92208</v>
@@ -997,14 +1016,14 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Dalvastjärnen, Dalvastjärnen, Pi lm</t>
+          <t>Badtsavárrie, Badtsavárrie, Pi lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>624423</v>
+        <v>624395</v>
       </c>
       <c r="R5" t="n">
-        <v>7298332</v>
+        <v>7298485</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,7 +1082,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118942598</v>
+        <v>118942381</v>
       </c>
       <c r="B6" t="n">
         <v>92208</v>
@@ -1098,10 +1117,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>624471</v>
+        <v>624423</v>
       </c>
       <c r="R6" t="n">
-        <v>7298339</v>
+        <v>7298332</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,10 +1179,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118936785</v>
+        <v>118942598</v>
       </c>
       <c r="B7" t="n">
-        <v>79406</v>
+        <v>92208</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,21 +1190,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>864</v>
+        <v>658</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1214,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>624687</v>
+        <v>624471</v>
       </c>
       <c r="R7" t="n">
-        <v>7298499</v>
+        <v>7298339</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1241,26 +1260,6 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Bark of dead wood # Picea abies</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1277,7 +1276,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118939241</v>
+        <v>118936785</v>
       </c>
       <c r="B8" t="n">
         <v>79406</v>
@@ -1308,14 +1307,14 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Balkisberg, Balkisberg, Pi lm</t>
+          <t>Dalvastjärnen, Dalvastjärnen, Pi lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>624606</v>
+        <v>624687</v>
       </c>
       <c r="R8" t="n">
-        <v>7298605</v>
+        <v>7298499</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1358,6 +1357,26 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Picea abies</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1374,7 +1393,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118939884</v>
+        <v>118939241</v>
       </c>
       <c r="B9" t="n">
         <v>79406</v>
@@ -1409,10 +1428,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>624593</v>
+        <v>624606</v>
       </c>
       <c r="R9" t="n">
-        <v>7298603</v>
+        <v>7298605</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1455,26 +1474,6 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>glasbjörk</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Betula pubescens</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Betula pubescens</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1491,7 +1490,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118941737</v>
+        <v>118939884</v>
       </c>
       <c r="B10" t="n">
         <v>79406</v>
@@ -1522,14 +1521,14 @@
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Badtsavárrie, Badtsavárrie, Pi lm</t>
+          <t>Balkisberg, Balkisberg, Pi lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>624401</v>
+        <v>624593</v>
       </c>
       <c r="R10" t="n">
-        <v>7298508</v>
+        <v>7298603</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1572,6 +1571,26 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>glasbjörk</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Betula pubescens</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Betula pubescens</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1588,10 +1607,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118940084</v>
+        <v>118941737</v>
       </c>
       <c r="B11" t="n">
-        <v>91905</v>
+        <v>79406</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1599,34 +1618,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1108</v>
+        <v>864</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Balkisberg, Balkisberg, Pi lm</t>
+          <t>Badtsavárrie, Badtsavárrie, Pi lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>624586</v>
+        <v>624401</v>
       </c>
       <c r="R11" t="n">
-        <v>7298607</v>
+        <v>7298508</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1685,10 +1704,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118940936</v>
+        <v>135330023</v>
       </c>
       <c r="B12" t="n">
-        <v>91905</v>
+        <v>79452</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1696,37 +1715,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1108</v>
+        <v>864</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Balkisberg, Balkisberg, Pi lm</t>
+          <t>Balkisberg 260721, Pi lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>624506</v>
+        <v>624677</v>
       </c>
       <c r="R12" t="n">
-        <v>7298643</v>
+        <v>7298509</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1750,12 +1769,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-08-05</t>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-08-05</t>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1770,19 +1799,23 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Katharina Radloff</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr"/>
+          <t>Katharina Radloff</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118941669</v>
+        <v>118940084</v>
       </c>
       <c r="B13" t="n">
         <v>91905</v>
@@ -1817,10 +1850,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>624459</v>
+        <v>624586</v>
       </c>
       <c r="R13" t="n">
-        <v>7298537</v>
+        <v>7298607</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1879,7 +1912,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118941943</v>
+        <v>118940936</v>
       </c>
       <c r="B14" t="n">
         <v>91905</v>
@@ -1910,14 +1943,14 @@
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Badtsavárrie, Badtsavárrie, Pi lm</t>
+          <t>Balkisberg, Balkisberg, Pi lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>624292</v>
+        <v>624506</v>
       </c>
       <c r="R14" t="n">
-        <v>7298339</v>
+        <v>7298643</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1976,10 +2009,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118936910</v>
+        <v>118941669</v>
       </c>
       <c r="B15" t="n">
-        <v>91909</v>
+        <v>91905</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1987,21 +2020,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2011,10 +2044,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>624659</v>
+        <v>624459</v>
       </c>
       <c r="R15" t="n">
-        <v>7298524</v>
+        <v>7298537</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2073,10 +2106,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118938882</v>
+        <v>118941943</v>
       </c>
       <c r="B16" t="n">
-        <v>91909</v>
+        <v>91905</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2084,34 +2117,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Balkisberg, Balkisberg, Pi lm</t>
+          <t>Badtsavárrie, Badtsavárrie, Pi lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>624606</v>
+        <v>624292</v>
       </c>
       <c r="R16" t="n">
-        <v>7298573</v>
+        <v>7298339</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2170,10 +2203,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118941323</v>
+        <v>135330028</v>
       </c>
       <c r="B17" t="n">
-        <v>91909</v>
+        <v>91970</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2181,37 +2214,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Balkisberg, Balkisberg, Pi lm</t>
+          <t>Balkisberg 260721, Pi lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>624498</v>
+        <v>624491</v>
       </c>
       <c r="R17" t="n">
-        <v>7298629</v>
+        <v>7298616</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2235,12 +2268,27 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-08-05</t>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-08-05</t>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>12:38</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Granstubbe</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2249,25 +2297,30 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Katharina Radloff</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr"/>
+          <t>Katharina Radloff</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118942230</v>
+        <v>118936910</v>
       </c>
       <c r="B18" t="n">
         <v>91909</v>
@@ -2298,14 +2351,14 @@
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Dalvastjärnen, Dalvastjärnen, Pi lm</t>
+          <t>Balkisberg, Balkisberg, Pi lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>624391</v>
+        <v>624659</v>
       </c>
       <c r="R18" t="n">
-        <v>7298231</v>
+        <v>7298524</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2364,32 +2417,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118938454</v>
+        <v>118938882</v>
       </c>
       <c r="B19" t="n">
-        <v>91923</v>
+        <v>91909</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2399,10 +2452,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>624580</v>
+        <v>624606</v>
       </c>
       <c r="R19" t="n">
-        <v>7298577</v>
+        <v>7298573</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2461,45 +2514,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118941751</v>
+        <v>118941323</v>
       </c>
       <c r="B20" t="n">
-        <v>91923</v>
+        <v>91909</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Badtsavárrie, Badtsavárrie, Pi lm</t>
+          <t>Balkisberg, Balkisberg, Pi lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>624391</v>
+        <v>624498</v>
       </c>
       <c r="R20" t="n">
-        <v>7298510</v>
+        <v>7298629</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2558,10 +2611,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118938781</v>
+        <v>118942230</v>
       </c>
       <c r="B21" t="n">
-        <v>92369</v>
+        <v>91909</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2569,34 +2622,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Balkisberg, Balkisberg, Pi lm</t>
+          <t>Dalvastjärnen, Dalvastjärnen, Pi lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>624606</v>
+        <v>624391</v>
       </c>
       <c r="R21" t="n">
-        <v>7298573</v>
+        <v>7298231</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2639,26 +2692,6 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -2675,45 +2708,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118941779</v>
+        <v>118938454</v>
       </c>
       <c r="B22" t="n">
-        <v>92369</v>
+        <v>91923</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1209</v>
+        <v>1204</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Badtsavárrie, Badtsavárrie, Pi lm</t>
+          <t>Balkisberg, Balkisberg, Pi lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>624395</v>
+        <v>624580</v>
       </c>
       <c r="R22" t="n">
-        <v>7298485</v>
+        <v>7298577</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2772,45 +2805,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>118936855</v>
+        <v>118941751</v>
       </c>
       <c r="B23" t="n">
-        <v>83173</v>
+        <v>91923</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1312</v>
+        <v>1204</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Dalvastjärnen, Dalvastjärnen, Pi lm</t>
+          <t>Badtsavárrie, Badtsavárrie, Pi lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>624670</v>
+        <v>624391</v>
       </c>
       <c r="R23" t="n">
-        <v>7298506</v>
+        <v>7298510</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2853,26 +2886,6 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Picea abies</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -2889,48 +2902,48 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>118936973</v>
+        <v>135330030</v>
       </c>
       <c r="B24" t="n">
-        <v>83173</v>
+        <v>91988</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1312</v>
+        <v>1204</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Dalvastjärnen, Dalvastjärnen, Pi lm</t>
+          <t>Balkisberg 260721, Pi lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>624645</v>
+        <v>624435</v>
       </c>
       <c r="R24" t="n">
-        <v>7298510</v>
+        <v>7298389</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -2954,12 +2967,27 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-08-05</t>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-08-05</t>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>13:41</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Hård kant på gran/slät på tall, svart linje</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2974,60 +3002,64 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Katharina Radloff</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY24" t="inlineStr"/>
+          <t>Katharina Radloff</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>118938545</v>
+        <v>135330031</v>
       </c>
       <c r="B25" t="n">
-        <v>83173</v>
+        <v>91988</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1312</v>
+        <v>1204</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Balkisberg, Balkisberg, Pi lm</t>
+          <t>Balkisberg 260721, Pi lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>624578</v>
+        <v>624351</v>
       </c>
       <c r="R25" t="n">
-        <v>7298576</v>
+        <v>7298434</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3051,12 +3083,27 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-08-05</t>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-08-05</t>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>13:41</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Hård kant på gran, slät på tall, svart linje</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3071,22 +3118,26 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Katharina Radloff</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY25" t="inlineStr"/>
+          <t>Katharina Radloff</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>118941803</v>
+        <v>118938781</v>
       </c>
       <c r="B26" t="n">
-        <v>83173</v>
+        <v>92369</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3094,34 +3145,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1312</v>
+        <v>1209</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Dalvastjärnen, Dalvastjärnen, Pi lm</t>
+          <t>Balkisberg, Balkisberg, Pi lm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>624381</v>
+        <v>624606</v>
       </c>
       <c r="R26" t="n">
-        <v>7298418</v>
+        <v>7298573</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3164,6 +3215,26 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM26" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3180,10 +3251,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>118942069</v>
+        <v>118941779</v>
       </c>
       <c r="B27" t="n">
-        <v>83173</v>
+        <v>92369</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3191,34 +3262,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1312</v>
+        <v>1209</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Tjakttjure, Tjakttjure, Pi lm</t>
+          <t>Badtsavárrie, Badtsavárrie, Pi lm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>624287</v>
+        <v>624395</v>
       </c>
       <c r="R27" t="n">
-        <v>7298315</v>
+        <v>7298485</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3277,7 +3348,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>118942308</v>
+        <v>118936855</v>
       </c>
       <c r="B28" t="n">
         <v>83173</v>
@@ -3312,10 +3383,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>624431</v>
+        <v>624670</v>
       </c>
       <c r="R28" t="n">
-        <v>7298295</v>
+        <v>7298506</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3358,6 +3429,26 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM28" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Picea abies</t>
+        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
@@ -3374,7 +3465,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>118942862</v>
+        <v>118936973</v>
       </c>
       <c r="B29" t="n">
         <v>83173</v>
@@ -3409,10 +3500,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>624490</v>
+        <v>624645</v>
       </c>
       <c r="R29" t="n">
-        <v>7298470</v>
+        <v>7298510</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3471,7 +3562,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>118942942</v>
+        <v>118938545</v>
       </c>
       <c r="B30" t="n">
         <v>83173</v>
@@ -3506,10 +3597,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>624582</v>
+        <v>624578</v>
       </c>
       <c r="R30" t="n">
-        <v>7298506</v>
+        <v>7298576</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3568,45 +3659,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>118941605</v>
+        <v>118941803</v>
       </c>
       <c r="B31" t="n">
-        <v>92292</v>
+        <v>83173</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1506</v>
+        <v>1312</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Balkisberg, Balkisberg, Pi lm</t>
+          <t>Dalvastjärnen, Dalvastjärnen, Pi lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>624497</v>
+        <v>624381</v>
       </c>
       <c r="R31" t="n">
-        <v>7298652</v>
+        <v>7298418</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3649,26 +3740,6 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
@@ -3685,45 +3756,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>118942590</v>
+        <v>118942069</v>
       </c>
       <c r="B32" t="n">
-        <v>92292</v>
+        <v>83173</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1506</v>
+        <v>1312</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Dalvastjärnen, Dalvastjärnen, Pi lm</t>
+          <t>Tjakttjure, Tjakttjure, Pi lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>624471</v>
+        <v>624287</v>
       </c>
       <c r="R32" t="n">
-        <v>7298339</v>
+        <v>7298315</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3782,10 +3853,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>118941838</v>
+        <v>118942308</v>
       </c>
       <c r="B33" t="n">
-        <v>80433</v>
+        <v>83173</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3793,21 +3864,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2081</v>
+        <v>1312</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3817,10 +3888,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>624377</v>
+        <v>624431</v>
       </c>
       <c r="R33" t="n">
-        <v>7298392</v>
+        <v>7298295</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3863,26 +3934,6 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
@@ -3899,32 +3950,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>118942181</v>
+        <v>118942862</v>
       </c>
       <c r="B34" t="n">
-        <v>92333</v>
+        <v>83173</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4217</v>
+        <v>1312</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3934,10 +3985,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>624369</v>
+        <v>624490</v>
       </c>
       <c r="R34" t="n">
-        <v>7298268</v>
+        <v>7298470</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3980,26 +4031,6 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ34" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK34" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
@@ -4016,45 +4047,45 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>118942694</v>
+        <v>118942942</v>
       </c>
       <c r="B35" t="n">
-        <v>91872</v>
+        <v>83173</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5447</v>
+        <v>1312</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Dalvastjärnen, Dalvastjärnen, Pi lm</t>
+          <t>Balkisberg, Balkisberg, Pi lm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>624468</v>
+        <v>624582</v>
       </c>
       <c r="R35" t="n">
-        <v>7298362</v>
+        <v>7298506</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4113,48 +4144,48 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>118936726</v>
+        <v>135330024</v>
       </c>
       <c r="B36" t="n">
-        <v>79327</v>
+        <v>83222</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Dalvastjärnen, Dalvastjärnen, Pi lm</t>
+          <t>Balkisberg 260721, Pi lm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>624698</v>
+        <v>624677</v>
       </c>
       <c r="R36" t="n">
-        <v>7298510</v>
+        <v>7298509</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4178,12 +4209,22 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2024-08-05</t>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2024-08-05</t>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4192,48 +4233,33 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ36" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK36" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO36" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Katharina Radloff</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY36" t="inlineStr"/>
+          <t>Katharina Radloff</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>118936878</v>
+        <v>118941605</v>
       </c>
       <c r="B37" t="n">
-        <v>79327</v>
+        <v>92292</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4241,21 +4267,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>1506</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4265,10 +4291,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>624645</v>
+        <v>624497</v>
       </c>
       <c r="R37" t="n">
-        <v>7298514</v>
+        <v>7298652</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4311,6 +4337,26 @@
       </c>
       <c r="AG37" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM37" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
@@ -4327,10 +4373,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>118940575</v>
+        <v>118942590</v>
       </c>
       <c r="B38" t="n">
-        <v>79327</v>
+        <v>92292</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4338,34 +4384,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>1506</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Balkisberg, Balkisberg, Pi lm</t>
+          <t>Dalvastjärnen, Dalvastjärnen, Pi lm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>624545</v>
+        <v>624471</v>
       </c>
       <c r="R38" t="n">
-        <v>7298672</v>
+        <v>7298339</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4424,45 +4470,45 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>118941713</v>
+        <v>118941838</v>
       </c>
       <c r="B39" t="n">
-        <v>79327</v>
+        <v>80433</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Balkisberg, Balkisberg, Pi lm</t>
+          <t>Dalvastjärnen, Dalvastjärnen, Pi lm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>624408</v>
+        <v>624377</v>
       </c>
       <c r="R39" t="n">
-        <v>7298513</v>
+        <v>7298392</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4505,6 +4551,26 @@
       </c>
       <c r="AG39" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM39" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
@@ -4521,45 +4587,45 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>118942067</v>
+        <v>118942181</v>
       </c>
       <c r="B40" t="n">
-        <v>79327</v>
+        <v>92333</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>4217</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Tjakttjure, Tjakttjure, Pi lm</t>
+          <t>Dalvastjärnen, Dalvastjärnen, Pi lm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>624287</v>
+        <v>624369</v>
       </c>
       <c r="R40" t="n">
-        <v>7298315</v>
+        <v>7298268</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4602,6 +4668,26 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM40" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
@@ -4618,45 +4704,45 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>118942245</v>
+        <v>118942694</v>
       </c>
       <c r="B41" t="n">
-        <v>79327</v>
+        <v>91872</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Tjakttjure, Tjakttjure, Pi lm</t>
+          <t>Dalvastjärnen, Dalvastjärnen, Pi lm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>624392</v>
+        <v>624468</v>
       </c>
       <c r="R41" t="n">
-        <v>7298198</v>
+        <v>7298362</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4715,48 +4801,48 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>118942784</v>
+        <v>135330029</v>
       </c>
       <c r="B42" t="n">
-        <v>79327</v>
+        <v>91937</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Dalvastjärnen, Dalvastjärnen, Pi lm</t>
+          <t>Balkisberg 260721, Pi lm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>624426</v>
+        <v>624435</v>
       </c>
       <c r="R42" t="n">
-        <v>7298414</v>
+        <v>7298389</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4780,12 +4866,27 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2024-08-05</t>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2024-08-05</t>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>13:29</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Växar på gran /tall. Lederlukt</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4800,19 +4901,23 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Katharina Radloff</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY42" t="inlineStr"/>
+          <t>Katharina Radloff</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>118942910</v>
+        <v>118936726</v>
       </c>
       <c r="B43" t="n">
         <v>79327</v>
@@ -4843,14 +4948,14 @@
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Balkisberg, Balkisberg, Pi lm</t>
+          <t>Dalvastjärnen, Dalvastjärnen, Pi lm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>624550</v>
+        <v>624698</v>
       </c>
       <c r="R43" t="n">
-        <v>7298507</v>
+        <v>7298510</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4893,6 +4998,26 @@
       </c>
       <c r="AG43" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM43" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
@@ -4909,45 +5034,45 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>118941845</v>
+        <v>118936878</v>
       </c>
       <c r="B44" t="n">
-        <v>80468</v>
+        <v>79327</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Dalvastjärnen, Dalvastjärnen, Pi lm</t>
+          <t>Balkisberg, Balkisberg, Pi lm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>624377</v>
+        <v>624645</v>
       </c>
       <c r="R44" t="n">
-        <v>7298392</v>
+        <v>7298514</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5006,45 +5131,45 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>118942330</v>
+        <v>118940575</v>
       </c>
       <c r="B45" t="n">
-        <v>80468</v>
+        <v>79327</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Dalvastjärnen, Dalvastjärnen, Pi lm</t>
+          <t>Balkisberg, Balkisberg, Pi lm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>624458</v>
+        <v>624545</v>
       </c>
       <c r="R45" t="n">
-        <v>7298303</v>
+        <v>7298672</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5103,50 +5228,45 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>118937317</v>
+        <v>118941713</v>
       </c>
       <c r="B46" t="n">
-        <v>57953</v>
+        <v>79327</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Balkisberg, Balkisberg, Pi lm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>624629</v>
+        <v>624408</v>
       </c>
       <c r="R46" t="n">
-        <v>7298517</v>
+        <v>7298513</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5202,6 +5322,1033 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>118942067</v>
+      </c>
+      <c r="B47" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Tjakttjure, Tjakttjure, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>624287</v>
+      </c>
+      <c r="R47" t="n">
+        <v>7298315</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2024-08-05</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2024-08-05</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>118942245</v>
+      </c>
+      <c r="B48" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Tjakttjure, Tjakttjure, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>624392</v>
+      </c>
+      <c r="R48" t="n">
+        <v>7298198</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2024-08-05</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2024-08-05</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>118942784</v>
+      </c>
+      <c r="B49" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Dalvastjärnen, Dalvastjärnen, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>624426</v>
+      </c>
+      <c r="R49" t="n">
+        <v>7298414</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2024-08-05</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2024-08-05</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>118942910</v>
+      </c>
+      <c r="B50" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Balkisberg, Balkisberg, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>624550</v>
+      </c>
+      <c r="R50" t="n">
+        <v>7298507</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2024-08-05</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2024-08-05</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>135330033</v>
+      </c>
+      <c r="B51" t="n">
+        <v>80493</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Balkisberg 260721, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>624501</v>
+      </c>
+      <c r="R51" t="n">
+        <v>7298369</v>
+      </c>
+      <c r="S51" t="n">
+        <v>13</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>14:26</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>14:26</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Inga vita papiller under, slät, vit i delningen</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Katharina Radloff</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Katharina Radloff</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>135330026</v>
+      </c>
+      <c r="B52" t="n">
+        <v>80499</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Balkisberg 260721, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>624628</v>
+      </c>
+      <c r="R52" t="n">
+        <v>7298521</v>
+      </c>
+      <c r="S52" t="n">
+        <v>5</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>12:12</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>12:12</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Sälg asp rönn</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Katharina Radloff</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Katharina Radloff</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>118941845</v>
+      </c>
+      <c r="B53" t="n">
+        <v>80468</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Dalvastjärnen, Dalvastjärnen, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>624377</v>
+      </c>
+      <c r="R53" t="n">
+        <v>7298392</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2024-08-05</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2024-08-05</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>118942330</v>
+      </c>
+      <c r="B54" t="n">
+        <v>80468</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Dalvastjärnen, Dalvastjärnen, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>624458</v>
+      </c>
+      <c r="R54" t="n">
+        <v>7298303</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2024-08-05</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2024-08-05</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>135330025</v>
+      </c>
+      <c r="B55" t="n">
+        <v>80500</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Balkisberg 260721, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>624628</v>
+      </c>
+      <c r="R55" t="n">
+        <v>7298521</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>12:12</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>12:12</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Katharina Radloff</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Katharina Radloff</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>118937317</v>
+      </c>
+      <c r="B56" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Balkisberg, Balkisberg, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>624629</v>
+      </c>
+      <c r="R56" t="n">
+        <v>7298517</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2024-08-05</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2024-08-05</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 64805-2023 artfynd.xlsx
+++ b/artfynd/A 64805-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY56"/>
+  <dimension ref="A1:AZ56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -788,6 +793,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135330034</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -885,6 +895,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118938830</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -982,6 +997,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118941656</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1079,6 +1099,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118941785</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1176,6 +1201,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118942381</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1273,6 +1303,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118942598</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1390,6 +1425,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118936785</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1487,6 +1527,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118939241</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1604,6 +1649,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118939884</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1701,6 +1751,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118941737</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1812,6 +1867,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135330023</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1909,6 +1969,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118940084</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2006,6 +2071,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118940936</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2103,6 +2173,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118941669</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2200,6 +2275,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118941943</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2317,6 +2397,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135330028</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2414,6 +2499,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118936910</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2511,6 +2601,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118938882</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2608,6 +2703,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118941323</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2705,6 +2805,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118942230</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2802,6 +2907,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118938454</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2899,6 +3009,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118941751</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3015,6 +3130,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135330030</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3131,6 +3251,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135330031</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3248,6 +3373,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118938781</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3345,6 +3475,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118941779</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3462,6 +3597,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118936855</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3559,6 +3699,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118936973</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3656,6 +3801,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118938545</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3753,6 +3903,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118941803</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3850,6 +4005,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118942069</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3947,6 +4107,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118942308</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4044,6 +4209,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118942862</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4141,6 +4311,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118942942</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4253,6 +4428,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135330024</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4370,6 +4550,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118941605</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4467,6 +4652,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118942590</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4584,6 +4774,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118941838</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4701,6 +4896,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118942181</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4798,6 +4998,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118942694</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4914,6 +5119,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135330029</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5031,6 +5241,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118936726</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5128,6 +5343,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118936878</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5225,6 +5445,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118940575</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5322,6 +5547,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118941713</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5419,6 +5649,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118942067</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5516,6 +5751,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118942245</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5613,6 +5853,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118942784</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5710,6 +5955,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118942910</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5826,6 +6076,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135330033</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5942,6 +6197,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135330026</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6039,6 +6299,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118941845</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6136,6 +6401,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118942330</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6247,6 +6517,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135330025</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6349,8 +6624,70 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118937317</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 64805-2023 artfynd.xlsx
+++ b/artfynd/A 64805-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135330034</v>
       </c>
       <c r="B2" t="n">
-        <v>97435</v>
+        <v>97479</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1762,7 +1762,7 @@
         <v>135330023</v>
       </c>
       <c r="B12" t="n">
-        <v>79452</v>
+        <v>79490</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2286,7 +2286,7 @@
         <v>135330028</v>
       </c>
       <c r="B17" t="n">
-        <v>91970</v>
+        <v>92012</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -3020,7 +3020,7 @@
         <v>135330030</v>
       </c>
       <c r="B24" t="n">
-        <v>91988</v>
+        <v>92030</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3141,7 +3141,7 @@
         <v>135330031</v>
       </c>
       <c r="B25" t="n">
-        <v>91988</v>
+        <v>92030</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -4322,7 +4322,7 @@
         <v>135330024</v>
       </c>
       <c r="B36" t="n">
-        <v>83222</v>
+        <v>83262</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5009,7 +5009,7 @@
         <v>135330029</v>
       </c>
       <c r="B42" t="n">
-        <v>91937</v>
+        <v>91979</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5966,7 +5966,7 @@
         <v>135330033</v>
       </c>
       <c r="B51" t="n">
-        <v>80493</v>
+        <v>80531</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6087,7 +6087,7 @@
         <v>135330026</v>
       </c>
       <c r="B52" t="n">
-        <v>80499</v>
+        <v>80537</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6412,7 +6412,7 @@
         <v>135330025</v>
       </c>
       <c r="B55" t="n">
-        <v>80500</v>
+        <v>80538</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>

--- a/artfynd/A 64805-2023 artfynd.xlsx
+++ b/artfynd/A 64805-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135330034</v>
       </c>
       <c r="B2" t="n">
-        <v>97479</v>
+        <v>97506</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1762,7 +1762,7 @@
         <v>135330023</v>
       </c>
       <c r="B12" t="n">
-        <v>79490</v>
+        <v>79517</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2286,7 +2286,7 @@
         <v>135330028</v>
       </c>
       <c r="B17" t="n">
-        <v>92012</v>
+        <v>92039</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -3020,7 +3020,7 @@
         <v>135330030</v>
       </c>
       <c r="B24" t="n">
-        <v>92030</v>
+        <v>92057</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3141,7 +3141,7 @@
         <v>135330031</v>
       </c>
       <c r="B25" t="n">
-        <v>92030</v>
+        <v>92057</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -4322,7 +4322,7 @@
         <v>135330024</v>
       </c>
       <c r="B36" t="n">
-        <v>83262</v>
+        <v>83289</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5009,7 +5009,7 @@
         <v>135330029</v>
       </c>
       <c r="B42" t="n">
-        <v>91979</v>
+        <v>92006</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5966,7 +5966,7 @@
         <v>135330033</v>
       </c>
       <c r="B51" t="n">
-        <v>80531</v>
+        <v>80558</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6087,7 +6087,7 @@
         <v>135330026</v>
       </c>
       <c r="B52" t="n">
-        <v>80537</v>
+        <v>80564</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6412,7 +6412,7 @@
         <v>135330025</v>
       </c>
       <c r="B55" t="n">
-        <v>80538</v>
+        <v>80565</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>

--- a/artfynd/A 64805-2023 artfynd.xlsx
+++ b/artfynd/A 64805-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ46"/>
+  <dimension ref="A1:AZ56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118938830</v>
+        <v>135330034</v>
       </c>
       <c r="B2" t="n">
-        <v>92208</v>
+        <v>97511</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>658</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Balkisberg, Balkisberg, Pi lm</t>
+          <t>Balkisberg 260721, Pi lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>624606</v>
+        <v>624594</v>
       </c>
       <c r="R2" t="n">
-        <v>7298573</v>
+        <v>7298492</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,12 +745,27 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-08-05</t>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-08-05</t>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Grön röd brun</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,24 +780,28 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Katharina Radloff</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>Katharina Radloff</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118938830</t>
+          <t>https://artportalen.se/Sighting/135330034</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118941656</v>
+        <v>118938830</v>
       </c>
       <c r="B3" t="n">
         <v>92208</v>
@@ -817,10 +836,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>624479</v>
+        <v>624606</v>
       </c>
       <c r="R3" t="n">
-        <v>7298572</v>
+        <v>7298573</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -878,13 +897,13 @@
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118941656</t>
+          <t>https://artportalen.se/Sighting/118938830</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118941785</v>
+        <v>118941656</v>
       </c>
       <c r="B4" t="n">
         <v>92208</v>
@@ -915,14 +934,14 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Badtsavárrie, Badtsavárrie, Pi lm</t>
+          <t>Balkisberg, Balkisberg, Pi lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>624395</v>
+        <v>624479</v>
       </c>
       <c r="R4" t="n">
-        <v>7298485</v>
+        <v>7298572</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -980,13 +999,13 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118941785</t>
+          <t>https://artportalen.se/Sighting/118941656</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118942381</v>
+        <v>118941785</v>
       </c>
       <c r="B5" t="n">
         <v>92208</v>
@@ -1017,14 +1036,14 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Dalvastjärnen, Dalvastjärnen, Pi lm</t>
+          <t>Badtsavárrie, Badtsavárrie, Pi lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>624423</v>
+        <v>624395</v>
       </c>
       <c r="R5" t="n">
-        <v>7298332</v>
+        <v>7298485</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1082,13 +1101,13 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118942381</t>
+          <t>https://artportalen.se/Sighting/118941785</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118942598</v>
+        <v>118942381</v>
       </c>
       <c r="B6" t="n">
         <v>92208</v>
@@ -1123,10 +1142,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>624471</v>
+        <v>624423</v>
       </c>
       <c r="R6" t="n">
-        <v>7298339</v>
+        <v>7298332</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1184,16 +1203,16 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118942598</t>
+          <t>https://artportalen.se/Sighting/118942381</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118936785</v>
+        <v>118942598</v>
       </c>
       <c r="B7" t="n">
-        <v>79406</v>
+        <v>92208</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1201,21 +1220,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>864</v>
+        <v>658</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1244,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>624687</v>
+        <v>624471</v>
       </c>
       <c r="R7" t="n">
-        <v>7298499</v>
+        <v>7298339</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1272,26 +1291,6 @@
       <c r="AG7" t="b">
         <v>0</v>
       </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Bark of dead wood # Picea abies</t>
-        </is>
-      </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
@@ -1306,13 +1305,13 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118936785</t>
+          <t>https://artportalen.se/Sighting/118942598</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118939241</v>
+        <v>118936785</v>
       </c>
       <c r="B8" t="n">
         <v>79406</v>
@@ -1343,14 +1342,14 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Balkisberg, Balkisberg, Pi lm</t>
+          <t>Dalvastjärnen, Dalvastjärnen, Pi lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>624606</v>
+        <v>624687</v>
       </c>
       <c r="R8" t="n">
-        <v>7298605</v>
+        <v>7298499</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1394,6 +1393,26 @@
       <c r="AG8" t="b">
         <v>0</v>
       </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Picea abies</t>
+        </is>
+      </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
@@ -1408,13 +1427,13 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118939241</t>
+          <t>https://artportalen.se/Sighting/118936785</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118939884</v>
+        <v>118939241</v>
       </c>
       <c r="B9" t="n">
         <v>79406</v>
@@ -1449,10 +1468,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>624593</v>
+        <v>624606</v>
       </c>
       <c r="R9" t="n">
-        <v>7298603</v>
+        <v>7298605</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1496,26 +1515,6 @@
       <c r="AG9" t="b">
         <v>0</v>
       </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>glasbjörk</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Betula pubescens</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Betula pubescens</t>
-        </is>
-      </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
@@ -1530,13 +1529,13 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118939884</t>
+          <t>https://artportalen.se/Sighting/118939241</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118941737</v>
+        <v>118939884</v>
       </c>
       <c r="B10" t="n">
         <v>79406</v>
@@ -1567,14 +1566,14 @@
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Badtsavárrie, Badtsavárrie, Pi lm</t>
+          <t>Balkisberg, Balkisberg, Pi lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>624401</v>
+        <v>624593</v>
       </c>
       <c r="R10" t="n">
-        <v>7298508</v>
+        <v>7298603</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1618,6 +1617,26 @@
       <c r="AG10" t="b">
         <v>0</v>
       </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>glasbjörk</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Betula pubescens</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Betula pubescens</t>
+        </is>
+      </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
@@ -1632,16 +1651,16 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118941737</t>
+          <t>https://artportalen.se/Sighting/118939884</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118940084</v>
+        <v>118941737</v>
       </c>
       <c r="B11" t="n">
-        <v>91905</v>
+        <v>79406</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1649,34 +1668,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1108</v>
+        <v>864</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Balkisberg, Balkisberg, Pi lm</t>
+          <t>Badtsavárrie, Badtsavárrie, Pi lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>624586</v>
+        <v>624401</v>
       </c>
       <c r="R11" t="n">
-        <v>7298607</v>
+        <v>7298508</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1734,16 +1753,16 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118940084</t>
+          <t>https://artportalen.se/Sighting/118941737</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118940936</v>
+        <v>135330023</v>
       </c>
       <c r="B12" t="n">
-        <v>91905</v>
+        <v>79520</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1751,37 +1770,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1108</v>
+        <v>864</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Balkisberg, Balkisberg, Pi lm</t>
+          <t>Balkisberg 260721, Pi lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>624506</v>
+        <v>624677</v>
       </c>
       <c r="R12" t="n">
-        <v>7298643</v>
+        <v>7298509</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1805,12 +1824,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-08-05</t>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-08-05</t>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1825,24 +1854,28 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Katharina Radloff</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr"/>
+          <t>Katharina Radloff</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118940936</t>
+          <t>https://artportalen.se/Sighting/135330023</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118941669</v>
+        <v>118940084</v>
       </c>
       <c r="B13" t="n">
         <v>91905</v>
@@ -1877,10 +1910,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>624459</v>
+        <v>624586</v>
       </c>
       <c r="R13" t="n">
-        <v>7298537</v>
+        <v>7298607</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1938,13 +1971,13 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118941669</t>
+          <t>https://artportalen.se/Sighting/118940084</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118941943</v>
+        <v>118940936</v>
       </c>
       <c r="B14" t="n">
         <v>91905</v>
@@ -1975,14 +2008,14 @@
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Badtsavárrie, Badtsavárrie, Pi lm</t>
+          <t>Balkisberg, Balkisberg, Pi lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>624292</v>
+        <v>624506</v>
       </c>
       <c r="R14" t="n">
-        <v>7298339</v>
+        <v>7298643</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2040,16 +2073,16 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118941943</t>
+          <t>https://artportalen.se/Sighting/118940936</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118936910</v>
+        <v>118941669</v>
       </c>
       <c r="B15" t="n">
-        <v>91909</v>
+        <v>91905</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2057,21 +2090,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2081,10 +2114,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>624659</v>
+        <v>624459</v>
       </c>
       <c r="R15" t="n">
-        <v>7298524</v>
+        <v>7298537</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2142,16 +2175,16 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118936910</t>
+          <t>https://artportalen.se/Sighting/118941669</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118938882</v>
+        <v>118941943</v>
       </c>
       <c r="B16" t="n">
-        <v>91909</v>
+        <v>91905</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2159,34 +2192,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Balkisberg, Balkisberg, Pi lm</t>
+          <t>Badtsavárrie, Badtsavárrie, Pi lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>624606</v>
+        <v>624292</v>
       </c>
       <c r="R16" t="n">
-        <v>7298573</v>
+        <v>7298339</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2244,16 +2277,16 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118938882</t>
+          <t>https://artportalen.se/Sighting/118941943</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118941323</v>
+        <v>135330028</v>
       </c>
       <c r="B17" t="n">
-        <v>91909</v>
+        <v>92044</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2261,37 +2294,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Balkisberg, Balkisberg, Pi lm</t>
+          <t>Balkisberg 260721, Pi lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>624498</v>
+        <v>624491</v>
       </c>
       <c r="R17" t="n">
-        <v>7298629</v>
+        <v>7298616</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2315,12 +2348,27 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-08-05</t>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-08-05</t>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>12:38</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Granstubbe</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2329,30 +2377,35 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Katharina Radloff</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr"/>
+          <t>Katharina Radloff</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118941323</t>
+          <t>https://artportalen.se/Sighting/135330028</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118942230</v>
+        <v>118936910</v>
       </c>
       <c r="B18" t="n">
         <v>91909</v>
@@ -2383,14 +2436,14 @@
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Dalvastjärnen, Dalvastjärnen, Pi lm</t>
+          <t>Balkisberg, Balkisberg, Pi lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>624391</v>
+        <v>624659</v>
       </c>
       <c r="R18" t="n">
-        <v>7298231</v>
+        <v>7298524</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2448,38 +2501,38 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118942230</t>
+          <t>https://artportalen.se/Sighting/118936910</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118938454</v>
+        <v>118938882</v>
       </c>
       <c r="B19" t="n">
-        <v>91923</v>
+        <v>91909</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2489,10 +2542,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>624580</v>
+        <v>624606</v>
       </c>
       <c r="R19" t="n">
-        <v>7298577</v>
+        <v>7298573</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2550,51 +2603,51 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118938454</t>
+          <t>https://artportalen.se/Sighting/118938882</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118941751</v>
+        <v>118941323</v>
       </c>
       <c r="B20" t="n">
-        <v>91923</v>
+        <v>91909</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Badtsavárrie, Badtsavárrie, Pi lm</t>
+          <t>Balkisberg, Balkisberg, Pi lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>624391</v>
+        <v>624498</v>
       </c>
       <c r="R20" t="n">
-        <v>7298510</v>
+        <v>7298629</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2652,16 +2705,16 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118941751</t>
+          <t>https://artportalen.se/Sighting/118941323</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118938781</v>
+        <v>118942230</v>
       </c>
       <c r="B21" t="n">
-        <v>92369</v>
+        <v>91909</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2669,34 +2722,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Balkisberg, Balkisberg, Pi lm</t>
+          <t>Dalvastjärnen, Dalvastjärnen, Pi lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>624606</v>
+        <v>624391</v>
       </c>
       <c r="R21" t="n">
-        <v>7298573</v>
+        <v>7298231</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2740,26 +2793,6 @@
       <c r="AG21" t="b">
         <v>0</v>
       </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
-        </is>
-      </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
@@ -2774,51 +2807,51 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118938781</t>
+          <t>https://artportalen.se/Sighting/118942230</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118941779</v>
+        <v>118938454</v>
       </c>
       <c r="B22" t="n">
-        <v>92369</v>
+        <v>91923</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1209</v>
+        <v>1204</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Badtsavárrie, Badtsavárrie, Pi lm</t>
+          <t>Balkisberg, Balkisberg, Pi lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>624395</v>
+        <v>624580</v>
       </c>
       <c r="R22" t="n">
-        <v>7298485</v>
+        <v>7298577</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2876,51 +2909,51 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118941779</t>
+          <t>https://artportalen.se/Sighting/118938454</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>118936855</v>
+        <v>118941751</v>
       </c>
       <c r="B23" t="n">
-        <v>83173</v>
+        <v>91923</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1312</v>
+        <v>1204</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Dalvastjärnen, Dalvastjärnen, Pi lm</t>
+          <t>Badtsavárrie, Badtsavárrie, Pi lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>624670</v>
+        <v>624391</v>
       </c>
       <c r="R23" t="n">
-        <v>7298506</v>
+        <v>7298510</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2964,26 +2997,6 @@
       <c r="AG23" t="b">
         <v>0</v>
       </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Picea abies</t>
-        </is>
-      </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
@@ -2998,54 +3011,54 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118936855</t>
+          <t>https://artportalen.se/Sighting/118941751</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>118936973</v>
+        <v>135330030</v>
       </c>
       <c r="B24" t="n">
-        <v>83173</v>
+        <v>92062</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1312</v>
+        <v>1204</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Dalvastjärnen, Dalvastjärnen, Pi lm</t>
+          <t>Balkisberg 260721, Pi lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>624645</v>
+        <v>624435</v>
       </c>
       <c r="R24" t="n">
-        <v>7298510</v>
+        <v>7298389</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3069,12 +3082,27 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-08-05</t>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-08-05</t>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>13:41</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Hård kant på gran/slät på tall, svart linje</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3089,65 +3117,69 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Katharina Radloff</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY24" t="inlineStr"/>
+          <t>Katharina Radloff</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118936973</t>
+          <t>https://artportalen.se/Sighting/135330030</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>118938545</v>
+        <v>135330031</v>
       </c>
       <c r="B25" t="n">
-        <v>83173</v>
+        <v>92062</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1312</v>
+        <v>1204</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Balkisberg, Balkisberg, Pi lm</t>
+          <t>Balkisberg 260721, Pi lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>624578</v>
+        <v>624351</v>
       </c>
       <c r="R25" t="n">
-        <v>7298576</v>
+        <v>7298434</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3171,12 +3203,27 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-08-05</t>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-08-05</t>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>13:41</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Hård kant på gran, slät på tall, svart linje</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3191,27 +3238,31 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Katharina Radloff</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY25" t="inlineStr"/>
+          <t>Katharina Radloff</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118938545</t>
+          <t>https://artportalen.se/Sighting/135330031</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>118941803</v>
+        <v>118938781</v>
       </c>
       <c r="B26" t="n">
-        <v>83173</v>
+        <v>92369</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3219,34 +3270,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1312</v>
+        <v>1209</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Dalvastjärnen, Dalvastjärnen, Pi lm</t>
+          <t>Balkisberg, Balkisberg, Pi lm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>624381</v>
+        <v>624606</v>
       </c>
       <c r="R26" t="n">
-        <v>7298418</v>
+        <v>7298573</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3290,6 +3341,26 @@
       <c r="AG26" t="b">
         <v>0</v>
       </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM26" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
+        </is>
+      </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
@@ -3304,16 +3375,16 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118941803</t>
+          <t>https://artportalen.se/Sighting/118938781</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>118942069</v>
+        <v>118941779</v>
       </c>
       <c r="B27" t="n">
-        <v>83173</v>
+        <v>92369</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3321,34 +3392,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1312</v>
+        <v>1209</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Tjakttjure, Tjakttjure, Pi lm</t>
+          <t>Badtsavárrie, Badtsavárrie, Pi lm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>624287</v>
+        <v>624395</v>
       </c>
       <c r="R27" t="n">
-        <v>7298315</v>
+        <v>7298485</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3406,13 +3477,13 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118942069</t>
+          <t>https://artportalen.se/Sighting/118941779</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>118942308</v>
+        <v>118936855</v>
       </c>
       <c r="B28" t="n">
         <v>83173</v>
@@ -3447,10 +3518,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>624431</v>
+        <v>624670</v>
       </c>
       <c r="R28" t="n">
-        <v>7298295</v>
+        <v>7298506</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3494,6 +3565,26 @@
       <c r="AG28" t="b">
         <v>0</v>
       </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM28" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Picea abies</t>
+        </is>
+      </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
@@ -3508,13 +3599,13 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118942308</t>
+          <t>https://artportalen.se/Sighting/118936855</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>118942862</v>
+        <v>118936973</v>
       </c>
       <c r="B29" t="n">
         <v>83173</v>
@@ -3549,10 +3640,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>624490</v>
+        <v>624645</v>
       </c>
       <c r="R29" t="n">
-        <v>7298470</v>
+        <v>7298510</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3610,13 +3701,13 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118942862</t>
+          <t>https://artportalen.se/Sighting/118936973</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>118942942</v>
+        <v>118938545</v>
       </c>
       <c r="B30" t="n">
         <v>83173</v>
@@ -3651,10 +3742,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>624582</v>
+        <v>624578</v>
       </c>
       <c r="R30" t="n">
-        <v>7298506</v>
+        <v>7298576</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3712,51 +3803,51 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118942942</t>
+          <t>https://artportalen.se/Sighting/118938545</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>118941605</v>
+        <v>118941803</v>
       </c>
       <c r="B31" t="n">
-        <v>92292</v>
+        <v>83173</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1506</v>
+        <v>1312</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Balkisberg, Balkisberg, Pi lm</t>
+          <t>Dalvastjärnen, Dalvastjärnen, Pi lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>624497</v>
+        <v>624381</v>
       </c>
       <c r="R31" t="n">
-        <v>7298652</v>
+        <v>7298418</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3800,26 +3891,6 @@
       <c r="AG31" t="b">
         <v>0</v>
       </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
-        </is>
-      </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
@@ -3834,51 +3905,51 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118941605</t>
+          <t>https://artportalen.se/Sighting/118941803</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>118942590</v>
+        <v>118942069</v>
       </c>
       <c r="B32" t="n">
-        <v>92292</v>
+        <v>83173</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1506</v>
+        <v>1312</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Dalvastjärnen, Dalvastjärnen, Pi lm</t>
+          <t>Tjakttjure, Tjakttjure, Pi lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>624471</v>
+        <v>624287</v>
       </c>
       <c r="R32" t="n">
-        <v>7298339</v>
+        <v>7298315</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3936,16 +4007,16 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118942590</t>
+          <t>https://artportalen.se/Sighting/118942069</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>118941838</v>
+        <v>118942308</v>
       </c>
       <c r="B33" t="n">
-        <v>80433</v>
+        <v>83173</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3953,21 +4024,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2081</v>
+        <v>1312</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3977,10 +4048,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>624377</v>
+        <v>624431</v>
       </c>
       <c r="R33" t="n">
-        <v>7298392</v>
+        <v>7298295</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4024,26 +4095,6 @@
       <c r="AG33" t="b">
         <v>0</v>
       </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
-      </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
@@ -4058,38 +4109,38 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118941838</t>
+          <t>https://artportalen.se/Sighting/118942308</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>118942181</v>
+        <v>118942862</v>
       </c>
       <c r="B34" t="n">
-        <v>92333</v>
+        <v>83173</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4217</v>
+        <v>1312</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4099,10 +4150,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>624369</v>
+        <v>624490</v>
       </c>
       <c r="R34" t="n">
-        <v>7298268</v>
+        <v>7298470</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4146,26 +4197,6 @@
       <c r="AG34" t="b">
         <v>0</v>
       </c>
-      <c r="AJ34" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK34" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
-        </is>
-      </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
@@ -4180,51 +4211,51 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118942181</t>
+          <t>https://artportalen.se/Sighting/118942862</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>118942694</v>
+        <v>118942942</v>
       </c>
       <c r="B35" t="n">
-        <v>91872</v>
+        <v>83173</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5447</v>
+        <v>1312</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Dalvastjärnen, Dalvastjärnen, Pi lm</t>
+          <t>Balkisberg, Balkisberg, Pi lm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>624468</v>
+        <v>624582</v>
       </c>
       <c r="R35" t="n">
-        <v>7298362</v>
+        <v>7298506</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4282,54 +4313,54 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118942694</t>
+          <t>https://artportalen.se/Sighting/118942942</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>118936726</v>
+        <v>135330024</v>
       </c>
       <c r="B36" t="n">
-        <v>79327</v>
+        <v>83292</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Dalvastjärnen, Dalvastjärnen, Pi lm</t>
+          <t>Balkisberg 260721, Pi lm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>624698</v>
+        <v>624677</v>
       </c>
       <c r="R36" t="n">
-        <v>7298510</v>
+        <v>7298509</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4353,12 +4384,22 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2024-08-05</t>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2024-08-05</t>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4367,53 +4408,38 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ36" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK36" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO36" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Katharina Radloff</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY36" t="inlineStr"/>
+          <t>Katharina Radloff</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118936726</t>
+          <t>https://artportalen.se/Sighting/135330024</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>118936878</v>
+        <v>118941605</v>
       </c>
       <c r="B37" t="n">
-        <v>79327</v>
+        <v>92292</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4421,21 +4447,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>1506</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4445,10 +4471,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>624645</v>
+        <v>624497</v>
       </c>
       <c r="R37" t="n">
-        <v>7298514</v>
+        <v>7298652</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4492,6 +4518,26 @@
       <c r="AG37" t="b">
         <v>0</v>
       </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM37" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
+        </is>
+      </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
@@ -4506,16 +4552,16 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118936878</t>
+          <t>https://artportalen.se/Sighting/118941605</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>118940575</v>
+        <v>118942590</v>
       </c>
       <c r="B38" t="n">
-        <v>79327</v>
+        <v>92292</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4523,34 +4569,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>1506</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Balkisberg, Balkisberg, Pi lm</t>
+          <t>Dalvastjärnen, Dalvastjärnen, Pi lm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>624545</v>
+        <v>624471</v>
       </c>
       <c r="R38" t="n">
-        <v>7298672</v>
+        <v>7298339</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4608,51 +4654,51 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118940575</t>
+          <t>https://artportalen.se/Sighting/118942590</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>118941713</v>
+        <v>118941838</v>
       </c>
       <c r="B39" t="n">
-        <v>79327</v>
+        <v>80433</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Balkisberg, Balkisberg, Pi lm</t>
+          <t>Dalvastjärnen, Dalvastjärnen, Pi lm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>624408</v>
+        <v>624377</v>
       </c>
       <c r="R39" t="n">
-        <v>7298513</v>
+        <v>7298392</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4696,6 +4742,26 @@
       <c r="AG39" t="b">
         <v>0</v>
       </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM39" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
+      </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
@@ -4710,51 +4776,51 @@
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118941713</t>
+          <t>https://artportalen.se/Sighting/118941838</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>118942067</v>
+        <v>118942181</v>
       </c>
       <c r="B40" t="n">
-        <v>79327</v>
+        <v>92333</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>4217</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Tjakttjure, Tjakttjure, Pi lm</t>
+          <t>Dalvastjärnen, Dalvastjärnen, Pi lm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>624287</v>
+        <v>624369</v>
       </c>
       <c r="R40" t="n">
-        <v>7298315</v>
+        <v>7298268</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4798,6 +4864,26 @@
       <c r="AG40" t="b">
         <v>0</v>
       </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM40" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
+        </is>
+      </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
@@ -4812,51 +4898,51 @@
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118942067</t>
+          <t>https://artportalen.se/Sighting/118942181</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>118942245</v>
+        <v>118942694</v>
       </c>
       <c r="B41" t="n">
-        <v>79327</v>
+        <v>91872</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Tjakttjure, Tjakttjure, Pi lm</t>
+          <t>Dalvastjärnen, Dalvastjärnen, Pi lm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>624392</v>
+        <v>624468</v>
       </c>
       <c r="R41" t="n">
-        <v>7298198</v>
+        <v>7298362</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4914,54 +5000,54 @@
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118942245</t>
+          <t>https://artportalen.se/Sighting/118942694</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>118942784</v>
+        <v>135330029</v>
       </c>
       <c r="B42" t="n">
-        <v>79327</v>
+        <v>92011</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Dalvastjärnen, Dalvastjärnen, Pi lm</t>
+          <t>Balkisberg 260721, Pi lm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>624426</v>
+        <v>624435</v>
       </c>
       <c r="R42" t="n">
-        <v>7298414</v>
+        <v>7298389</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4985,12 +5071,27 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2024-08-05</t>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2024-08-05</t>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>13:29</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Växar på gran /tall. Lederlukt</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5005,24 +5106,28 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Katharina Radloff</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY42" t="inlineStr"/>
+          <t>Katharina Radloff</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118942784</t>
+          <t>https://artportalen.se/Sighting/135330029</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>118942910</v>
+        <v>118936726</v>
       </c>
       <c r="B43" t="n">
         <v>79327</v>
@@ -5053,14 +5158,14 @@
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Balkisberg, Balkisberg, Pi lm</t>
+          <t>Dalvastjärnen, Dalvastjärnen, Pi lm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>624550</v>
+        <v>624698</v>
       </c>
       <c r="R43" t="n">
-        <v>7298507</v>
+        <v>7298510</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5104,6 +5209,26 @@
       <c r="AG43" t="b">
         <v>0</v>
       </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM43" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
+      </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
@@ -5118,51 +5243,51 @@
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118942910</t>
+          <t>https://artportalen.se/Sighting/118936726</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>118941845</v>
+        <v>118936878</v>
       </c>
       <c r="B44" t="n">
-        <v>80468</v>
+        <v>79327</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Dalvastjärnen, Dalvastjärnen, Pi lm</t>
+          <t>Balkisberg, Balkisberg, Pi lm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>624377</v>
+        <v>624645</v>
       </c>
       <c r="R44" t="n">
-        <v>7298392</v>
+        <v>7298514</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5220,51 +5345,51 @@
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118941845</t>
+          <t>https://artportalen.se/Sighting/118936878</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>118942330</v>
+        <v>118940575</v>
       </c>
       <c r="B45" t="n">
-        <v>80468</v>
+        <v>79327</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Dalvastjärnen, Dalvastjärnen, Pi lm</t>
+          <t>Balkisberg, Balkisberg, Pi lm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>624458</v>
+        <v>624545</v>
       </c>
       <c r="R45" t="n">
-        <v>7298303</v>
+        <v>7298672</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5322,56 +5447,51 @@
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118942330</t>
+          <t>https://artportalen.se/Sighting/118940575</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>118937317</v>
+        <v>118941713</v>
       </c>
       <c r="B46" t="n">
-        <v>57953</v>
+        <v>79327</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Balkisberg, Balkisberg, Pi lm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>624629</v>
+        <v>624408</v>
       </c>
       <c r="R46" t="n">
-        <v>7298517</v>
+        <v>7298513</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5428,6 +5548,1083 @@
       </c>
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118941713</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>118942067</v>
+      </c>
+      <c r="B47" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Tjakttjure, Tjakttjure, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>624287</v>
+      </c>
+      <c r="R47" t="n">
+        <v>7298315</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2024-08-05</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2024-08-05</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118942067</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>118942245</v>
+      </c>
+      <c r="B48" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Tjakttjure, Tjakttjure, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>624392</v>
+      </c>
+      <c r="R48" t="n">
+        <v>7298198</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2024-08-05</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2024-08-05</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118942245</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>118942784</v>
+      </c>
+      <c r="B49" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Dalvastjärnen, Dalvastjärnen, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>624426</v>
+      </c>
+      <c r="R49" t="n">
+        <v>7298414</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2024-08-05</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2024-08-05</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118942784</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>118942910</v>
+      </c>
+      <c r="B50" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Balkisberg, Balkisberg, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>624550</v>
+      </c>
+      <c r="R50" t="n">
+        <v>7298507</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2024-08-05</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2024-08-05</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118942910</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>135330033</v>
+      </c>
+      <c r="B51" t="n">
+        <v>80561</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Balkisberg 260721, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>624501</v>
+      </c>
+      <c r="R51" t="n">
+        <v>7298369</v>
+      </c>
+      <c r="S51" t="n">
+        <v>13</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>14:26</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>14:26</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Inga vita papiller under, slät, vit i delningen</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Katharina Radloff</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Katharina Radloff</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135330033</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>135330026</v>
+      </c>
+      <c r="B52" t="n">
+        <v>80567</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Balkisberg 260721, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>624628</v>
+      </c>
+      <c r="R52" t="n">
+        <v>7298521</v>
+      </c>
+      <c r="S52" t="n">
+        <v>5</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>12:12</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>12:12</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Sälg asp rönn</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Katharina Radloff</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Katharina Radloff</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135330026</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>118941845</v>
+      </c>
+      <c r="B53" t="n">
+        <v>80468</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Dalvastjärnen, Dalvastjärnen, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>624377</v>
+      </c>
+      <c r="R53" t="n">
+        <v>7298392</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2024-08-05</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2024-08-05</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118941845</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>118942330</v>
+      </c>
+      <c r="B54" t="n">
+        <v>80468</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Dalvastjärnen, Dalvastjärnen, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>624458</v>
+      </c>
+      <c r="R54" t="n">
+        <v>7298303</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2024-08-05</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2024-08-05</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118942330</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>135330025</v>
+      </c>
+      <c r="B55" t="n">
+        <v>80568</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Balkisberg 260721, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>624628</v>
+      </c>
+      <c r="R55" t="n">
+        <v>7298521</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>12:12</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>12:12</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Katharina Radloff</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Katharina Radloff</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135330025</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>118937317</v>
+      </c>
+      <c r="B56" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Balkisberg, Balkisberg, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>624629</v>
+      </c>
+      <c r="R56" t="n">
+        <v>7298517</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2024-08-05</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2024-08-05</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/118937317</t>
         </is>
@@ -5480,6 +6677,16 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 64805-2023 artfynd.xlsx
+++ b/artfynd/A 64805-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135330034</v>
       </c>
       <c r="B2" t="n">
-        <v>97511</v>
+        <v>97513</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -2286,7 +2286,7 @@
         <v>135330028</v>
       </c>
       <c r="B17" t="n">
-        <v>92044</v>
+        <v>92046</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -3020,7 +3020,7 @@
         <v>135330030</v>
       </c>
       <c r="B24" t="n">
-        <v>92062</v>
+        <v>92064</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3141,7 +3141,7 @@
         <v>135330031</v>
       </c>
       <c r="B25" t="n">
-        <v>92062</v>
+        <v>92064</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -5009,7 +5009,7 @@
         <v>135330029</v>
       </c>
       <c r="B42" t="n">
-        <v>92011</v>
+        <v>92013</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
